--- a/Awin_Contacts_batch1.xlsx
+++ b/Awin_Contacts_batch1.xlsx
@@ -105,10 +105,10 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -752,43 +752,23 @@
       <c r="R5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Pablo</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Meca García</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
+      <c r="B6" s="2" t="inlineStr"/>
       <c r="C6" s="2" t="inlineStr"/>
       <c r="D6" s="2" t="inlineStr"/>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/pablo-meca-garcía-1b51a0231</t>
-        </is>
-      </c>
+      <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
           <t>365Rider</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Diseñador Gráfico y Asistente de Marketing Digital y Comunicación</t>
-        </is>
-      </c>
+      <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
           <t>365rider.com</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>es</t>
-        </is>
-      </c>
+      <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr">
         <is>
@@ -828,43 +808,23 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Alejandra</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Cuellar Quiles</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr"/>
       <c r="C7" s="2" t="inlineStr"/>
       <c r="D7" s="2" t="inlineStr"/>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/alejandra-cuellar-quiles-505633252</t>
-        </is>
-      </c>
+      <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="2" t="inlineStr">
         <is>
           <t>365Rider</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>Especialista en marketing digital</t>
-        </is>
-      </c>
+      <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
           <t>365rider.com</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>es</t>
-        </is>
-      </c>
+      <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr"/>
@@ -888,7 +848,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr"/>
       <c r="D8" s="3" t="inlineStr"/>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>https://linkedin.com/in/eunice-yang-713211204</t>
         </is>
@@ -1060,43 +1020,23 @@
       <c r="R11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Mario</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Federico</t>
-        </is>
-      </c>
+      <c r="A12" s="3" t="inlineStr"/>
+      <c r="B12" s="3" t="inlineStr"/>
       <c r="C12" s="3" t="inlineStr"/>
       <c r="D12" s="3" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/mario-federico-04a32a206</t>
-        </is>
-      </c>
+      <c r="E12" s="3" t="inlineStr"/>
       <c r="F12" s="3" t="inlineStr">
         <is>
           <t>50 ml IT</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>Performance Marketing Specialist</t>
-        </is>
-      </c>
+      <c r="G12" s="3" t="inlineStr"/>
       <c r="H12" s="3" t="inlineStr">
         <is>
           <t>50-ml.it</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>it</t>
-        </is>
-      </c>
+      <c r="I12" s="3" t="inlineStr"/>
       <c r="J12" s="3" t="inlineStr">
         <is>
           <t>30 Giorni</t>
@@ -1240,43 +1180,23 @@
       <c r="R15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Shawn</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Liu</t>
-        </is>
-      </c>
+      <c r="A16" s="3" t="inlineStr"/>
+      <c r="B16" s="3" t="inlineStr"/>
       <c r="C16" s="3" t="inlineStr"/>
       <c r="D16" s="3" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/shawn-liu-0b154855</t>
-        </is>
-      </c>
+      <c r="E16" s="3" t="inlineStr"/>
       <c r="F16" s="3" t="inlineStr">
         <is>
           <t>Acer IT</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>Head of Global Digital Marketing Transformation</t>
-        </is>
-      </c>
+      <c r="G16" s="3" t="inlineStr"/>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>acer.com</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>tw</t>
-        </is>
-      </c>
+          <t>store.acer.com</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr"/>
       <c r="J16" s="3" t="inlineStr">
         <is>
           <t>30 Giorni</t>
@@ -1312,43 +1232,23 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Filip</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Bekas</t>
-        </is>
-      </c>
+      <c r="A17" s="3" t="inlineStr"/>
+      <c r="B17" s="3" t="inlineStr"/>
       <c r="C17" s="3" t="inlineStr"/>
       <c r="D17" s="3" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/filip-bekas-04baab1b0</t>
-        </is>
-      </c>
+      <c r="E17" s="3" t="inlineStr"/>
       <c r="F17" s="3" t="inlineStr">
         <is>
           <t>Acer IT</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>Digital Marketing Manager</t>
-        </is>
-      </c>
+      <c r="G17" s="3" t="inlineStr"/>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>acer.com</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>pl</t>
-        </is>
-      </c>
+          <t>store.acer.com</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr"/>
       <c r="J17" s="3" t="inlineStr"/>
       <c r="K17" s="3" t="inlineStr"/>
       <c r="L17" s="3" t="inlineStr"/>
@@ -1856,7 +1756,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr"/>
       <c r="D30" s="2" t="inlineStr"/>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>https://linkedin.com/in/yaohui-dong-777z6181</t>
         </is>
@@ -1928,7 +1828,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr"/>
       <c r="D31" s="2" t="inlineStr"/>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>https://linkedin.com/in/axhart</t>
         </is>
@@ -1964,43 +1864,23 @@
       <c r="R31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>Vincenza</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>G.</t>
-        </is>
-      </c>
+      <c r="A32" s="3" t="inlineStr"/>
+      <c r="B32" s="3" t="inlineStr"/>
       <c r="C32" s="3" t="inlineStr"/>
       <c r="D32" s="3" t="inlineStr"/>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/vincenza-g-bbb9b8127</t>
-        </is>
-      </c>
+      <c r="E32" s="3" t="inlineStr"/>
       <c r="F32" s="3" t="inlineStr">
         <is>
           <t>Aliveda</t>
         </is>
       </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>Digital marketing e comunicazione</t>
-        </is>
-      </c>
+      <c r="G32" s="3" t="inlineStr"/>
       <c r="H32" s="3" t="inlineStr">
         <is>
           <t>aliveda.com</t>
         </is>
       </c>
-      <c r="I32" s="3" t="inlineStr">
-        <is>
-          <t>it</t>
-        </is>
-      </c>
+      <c r="I32" s="3" t="inlineStr"/>
       <c r="J32" s="3" t="inlineStr">
         <is>
           <t>30 Giorni</t>
@@ -2066,19 +1946,19 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Claudia</t>
+          <t>Matteo</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Dondi</t>
+          <t>Sonzogni, MBA</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr"/>
       <c r="D34" s="2" t="inlineStr"/>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/claudiadondi</t>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/matteosonzogni</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2088,12 +1968,12 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketing Manager</t>
+          <t>Digital Marketing Manager - Head of Web Programs</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>allianz.it</t>
+          <t>allianz.com</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2136,43 +2016,23 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>Giorgia</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>Yasmine Rocca</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr"/>
       <c r="D35" s="2" t="inlineStr"/>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/giorgiayasminerocca</t>
-        </is>
-      </c>
+      <c r="E35" s="2" t="inlineStr"/>
       <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Allianz Campaign 2025 IT</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>Digital Marketing Manager</t>
-        </is>
-      </c>
+      <c r="G35" s="2" t="inlineStr"/>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>allianz.it</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>it</t>
-        </is>
-      </c>
+          <t>allianz.com</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr"/>
@@ -2276,7 +2136,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr"/>
       <c r="D38" s="2" t="inlineStr"/>
-      <c r="E38" s="4" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>https://linkedin.com/in/vivian-wright-286531ba</t>
         </is>
@@ -2344,7 +2204,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr"/>
       <c r="D39" s="2" t="inlineStr"/>
-      <c r="E39" s="4" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>https://linkedin.com/in/patelchaitanya</t>
         </is>
@@ -2548,43 +2408,23 @@
       <c r="R43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>Luisa</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>Deagostino</t>
-        </is>
-      </c>
+      <c r="A44" s="3" t="inlineStr"/>
+      <c r="B44" s="3" t="inlineStr"/>
       <c r="C44" s="3" t="inlineStr"/>
       <c r="D44" s="3" t="inlineStr"/>
-      <c r="E44" s="5" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/luisa-deagostino-3b082616</t>
-        </is>
-      </c>
+      <c r="E44" s="3" t="inlineStr"/>
       <c r="F44" s="3" t="inlineStr">
         <is>
           <t>Alpitour IT</t>
         </is>
       </c>
-      <c r="G44" s="3" t="inlineStr">
-        <is>
-          <t>Corporate Digital Marketing</t>
-        </is>
-      </c>
+      <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="3" t="inlineStr">
         <is>
           <t>alpitour.it</t>
         </is>
       </c>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t>it</t>
-        </is>
-      </c>
+      <c r="I44" s="3" t="inlineStr"/>
       <c r="J44" s="3" t="inlineStr">
         <is>
           <t>30 Giorni</t>
@@ -2620,43 +2460,23 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>Stefano</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>Ponari</t>
-        </is>
-      </c>
+      <c r="A45" s="3" t="inlineStr"/>
+      <c r="B45" s="3" t="inlineStr"/>
       <c r="C45" s="3" t="inlineStr"/>
       <c r="D45" s="3" t="inlineStr"/>
-      <c r="E45" s="5" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/sponari</t>
-        </is>
-      </c>
+      <c r="E45" s="3" t="inlineStr"/>
       <c r="F45" s="3" t="inlineStr">
         <is>
           <t>Alpitour IT</t>
         </is>
       </c>
-      <c r="G45" s="3" t="inlineStr">
-        <is>
-          <t>Corporate Digital Marketing Strategist</t>
-        </is>
-      </c>
+      <c r="G45" s="3" t="inlineStr"/>
       <c r="H45" s="3" t="inlineStr">
         <is>
           <t>alpitour.it</t>
         </is>
       </c>
-      <c r="I45" s="3" t="inlineStr">
-        <is>
-          <t>it</t>
-        </is>
-      </c>
+      <c r="I45" s="3" t="inlineStr"/>
       <c r="J45" s="3" t="inlineStr"/>
       <c r="K45" s="3" t="inlineStr"/>
       <c r="L45" s="3" t="inlineStr"/>
@@ -3144,43 +2964,23 @@
       <c r="R57" s="3" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>Klaudia</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>Modelska</t>
-        </is>
-      </c>
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr"/>
       <c r="D58" s="2" t="inlineStr"/>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/klaudia-modelska</t>
-        </is>
-      </c>
+      <c r="E58" s="2" t="inlineStr"/>
       <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Answear IT</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>Senior Affiliate Marketing Specialist</t>
-        </is>
-      </c>
+      <c r="G58" s="2" t="inlineStr"/>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>answear.com</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>pl</t>
-        </is>
-      </c>
+          <t>answear.it</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr"/>
       <c r="J58" s="2" t="inlineStr">
         <is>
           <t>30 Giorni</t>
@@ -3212,43 +3012,23 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>👩🏻‍💻</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>Magdalena Albinska</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr"/>
       <c r="D59" s="2" t="inlineStr"/>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/albinska</t>
-        </is>
-      </c>
+      <c r="E59" s="2" t="inlineStr"/>
       <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Answear IT</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>E-commerce and Digital Marketing Director</t>
-        </is>
-      </c>
+      <c r="G59" s="2" t="inlineStr"/>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>answear.com</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>pl</t>
-        </is>
-      </c>
+          <t>answear.it</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr"/>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr"/>
@@ -3340,43 +3120,23 @@
       <c r="R61" s="3" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>Giampaolo</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>Montella</t>
-        </is>
-      </c>
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr"/>
       <c r="D62" s="2" t="inlineStr"/>
-      <c r="E62" s="4" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/giampaolo-montella-b2ab58147</t>
-        </is>
-      </c>
+      <c r="E62" s="2" t="inlineStr"/>
       <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Antony Morato IT</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>E-Commerce &amp; Digital Marketing</t>
-        </is>
-      </c>
+      <c r="G62" s="2" t="inlineStr"/>
       <c r="H62" s="2" t="inlineStr">
         <is>
           <t>antonymorato.com</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>it</t>
-        </is>
-      </c>
+      <c r="I62" s="2" t="inlineStr"/>
       <c r="J62" s="2" t="inlineStr">
         <is>
           <t>30 Giorni</t>
@@ -3412,43 +3172,23 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>Umberto</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>Formisano</t>
-        </is>
-      </c>
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr"/>
       <c r="D63" s="2" t="inlineStr"/>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/umberto-formisano-a7343121b</t>
-        </is>
-      </c>
+      <c r="E63" s="2" t="inlineStr"/>
       <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Antony Morato IT</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
-        <is>
-          <t>E-Commerce &amp; Digital Advertising</t>
-        </is>
-      </c>
+      <c r="G63" s="2" t="inlineStr"/>
       <c r="H63" s="2" t="inlineStr">
         <is>
           <t>antonymorato.com</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>it</t>
-        </is>
-      </c>
+      <c r="I63" s="2" t="inlineStr"/>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr"/>
@@ -3472,7 +3212,7 @@
       </c>
       <c r="C64" s="3" t="inlineStr"/>
       <c r="D64" s="3" t="inlineStr"/>
-      <c r="E64" s="5" t="inlineStr">
+      <c r="E64" s="4" t="inlineStr">
         <is>
           <t>https://linkedin.com/in/paolovalassi</t>
         </is>
@@ -3544,7 +3284,7 @@
       </c>
       <c r="C65" s="3" t="inlineStr"/>
       <c r="D65" s="3" t="inlineStr"/>
-      <c r="E65" s="5" t="inlineStr">
+      <c r="E65" s="4" t="inlineStr">
         <is>
           <t>https://linkedin.com/in/alessandraastarita</t>
         </is>
@@ -3756,7 +3496,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr"/>
       <c r="D70" s="2" t="inlineStr"/>
-      <c r="E70" s="4" t="inlineStr">
+      <c r="E70" s="5" t="inlineStr">
         <is>
           <t>https://linkedin.com/in/rosalbacaramia</t>
         </is>
@@ -3832,7 +3572,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr"/>
       <c r="D71" s="2" t="inlineStr"/>
-      <c r="E71" s="4" t="inlineStr">
+      <c r="E71" s="5" t="inlineStr">
         <is>
           <t>https://linkedin.com/in/paola-marotta-34b066211</t>
         </is>
@@ -4040,7 +3780,7 @@
       </c>
       <c r="C76" s="3" t="inlineStr"/>
       <c r="D76" s="3" t="inlineStr"/>
-      <c r="E76" s="5" t="inlineStr">
+      <c r="E76" s="4" t="inlineStr">
         <is>
           <t>https://linkedin.com/in/azizgazzella</t>
         </is>
@@ -4108,7 +3848,7 @@
       </c>
       <c r="C77" s="3" t="inlineStr"/>
       <c r="D77" s="3" t="inlineStr"/>
-      <c r="E77" s="5" t="inlineStr">
+      <c r="E77" s="4" t="inlineStr">
         <is>
           <t>https://linkedin.com/in/peter-schön-b7b138102</t>
         </is>
@@ -4624,43 +4364,23 @@
       <c r="R89" s="3" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>Mindora</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>Cowan</t>
-        </is>
-      </c>
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr"/>
       <c r="C90" s="2" t="inlineStr"/>
       <c r="D90" s="2" t="inlineStr"/>
-      <c r="E90" s="4" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/mindora-cowan-87783619</t>
-        </is>
-      </c>
+      <c r="E90" s="2" t="inlineStr"/>
       <c r="F90" s="2" t="inlineStr">
         <is>
           <t>Avon IT</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr">
-        <is>
-          <t>Affiliate Marketing Specialist</t>
-        </is>
-      </c>
+      <c r="G90" s="2" t="inlineStr"/>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>avon.com</t>
-        </is>
-      </c>
-      <c r="I90" s="2" t="inlineStr">
-        <is>
-          <t>us</t>
-        </is>
-      </c>
+          <t>avon.it</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr"/>
       <c r="J90" s="2" t="inlineStr">
         <is>
           <t>30 Giorni</t>
@@ -4696,43 +4416,23 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>Evelyn</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>Veras, M.B.A.</t>
-        </is>
-      </c>
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr"/>
       <c r="C91" s="2" t="inlineStr"/>
       <c r="D91" s="2" t="inlineStr"/>
-      <c r="E91" s="4" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/evelynverasmba</t>
-        </is>
-      </c>
+      <c r="E91" s="2" t="inlineStr"/>
       <c r="F91" s="2" t="inlineStr">
         <is>
           <t>Avon IT</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr">
-        <is>
-          <t>Digital Marketing Technology Manager</t>
-        </is>
-      </c>
+      <c r="G91" s="2" t="inlineStr"/>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>avon.com</t>
-        </is>
-      </c>
-      <c r="I91" s="2" t="inlineStr">
-        <is>
-          <t>us</t>
-        </is>
-      </c>
+          <t>avon.it</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr"/>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr"/>
@@ -4920,7 +4620,7 @@
       </c>
       <c r="C96" s="3" t="inlineStr"/>
       <c r="D96" s="3" t="inlineStr"/>
-      <c r="E96" s="5" t="inlineStr">
+      <c r="E96" s="4" t="inlineStr">
         <is>
           <t>https://linkedin.com/in/santiagomldl</t>
         </is>
@@ -4992,7 +4692,7 @@
       </c>
       <c r="C97" s="3" t="inlineStr"/>
       <c r="D97" s="3" t="inlineStr"/>
-      <c r="E97" s="5" t="inlineStr">
+      <c r="E97" s="4" t="inlineStr">
         <is>
           <t>https://linkedin.com/in/aurora-marchi-a11970263</t>
         </is>
@@ -5028,43 +4728,23 @@
       <c r="R97" s="3" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="inlineStr">
-        <is>
-          <t>Giulio</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>Ferracuti</t>
-        </is>
-      </c>
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr"/>
       <c r="C98" s="2" t="inlineStr"/>
       <c r="D98" s="2" t="inlineStr"/>
-      <c r="E98" s="4" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/giulioferracuti</t>
-        </is>
-      </c>
+      <c r="E98" s="2" t="inlineStr"/>
       <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Babbel IT</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr">
-        <is>
-          <t>Senior Affiliate Manager</t>
-        </is>
-      </c>
+      <c r="G98" s="2" t="inlineStr"/>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>babbel.com</t>
-        </is>
-      </c>
-      <c r="I98" s="2" t="inlineStr">
-        <is>
-          <t>de</t>
-        </is>
-      </c>
+          <t>it.babbel.com</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr"/>
       <c r="J98" s="2" t="inlineStr">
         <is>
           <t>30 Giorni</t>
@@ -5100,43 +4780,23 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="inlineStr">
-        <is>
-          <t>Pascal</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>Priso</t>
-        </is>
-      </c>
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr"/>
       <c r="C99" s="2" t="inlineStr"/>
       <c r="D99" s="2" t="inlineStr"/>
-      <c r="E99" s="4" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/pascal-priso-1753a460</t>
-        </is>
-      </c>
+      <c r="E99" s="2" t="inlineStr"/>
       <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Babbel IT</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr">
-        <is>
-          <t>Senior Performance Marketing Manager</t>
-        </is>
-      </c>
+      <c r="G99" s="2" t="inlineStr"/>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>babbel.com</t>
-        </is>
-      </c>
-      <c r="I99" s="2" t="inlineStr">
-        <is>
-          <t>de</t>
-        </is>
-      </c>
+          <t>it.babbel.com</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr"/>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr"/>
@@ -5228,43 +4888,23 @@
       <c r="R101" s="3" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>Chouaib</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>HIDARA</t>
-        </is>
-      </c>
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr"/>
       <c r="C102" s="2" t="inlineStr"/>
       <c r="D102" s="2" t="inlineStr"/>
-      <c r="E102" s="4" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/chouaib-hidara-4baa29130</t>
-        </is>
-      </c>
+      <c r="E102" s="2" t="inlineStr"/>
       <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Back Market IT</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr">
-        <is>
-          <t>Affiliate Marketing Manager</t>
-        </is>
-      </c>
+      <c r="G102" s="2" t="inlineStr"/>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>backmarket.com</t>
-        </is>
-      </c>
-      <c r="I102" s="2" t="inlineStr">
-        <is>
-          <t>fr</t>
-        </is>
-      </c>
+          <t>backmarket.it</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr"/>
       <c r="J102" s="2" t="inlineStr">
         <is>
           <t>30 Giorni</t>
@@ -5300,43 +4940,23 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>Emma</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>Gautier</t>
-        </is>
-      </c>
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr"/>
       <c r="C103" s="2" t="inlineStr"/>
       <c r="D103" s="2" t="inlineStr"/>
-      <c r="E103" s="4" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/emma-gautier-gem</t>
-        </is>
-      </c>
+      <c r="E103" s="2" t="inlineStr"/>
       <c r="F103" s="2" t="inlineStr">
         <is>
           <t>Back Market IT</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr">
-        <is>
-          <t>Performance Marketing | Affiliates</t>
-        </is>
-      </c>
+      <c r="G103" s="2" t="inlineStr"/>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>backmarket.com</t>
-        </is>
-      </c>
-      <c r="I103" s="2" t="inlineStr">
-        <is>
-          <t>fr</t>
-        </is>
-      </c>
+          <t>backmarket.it</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr"/>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr"/>
@@ -5988,7 +5608,7 @@
       </c>
       <c r="C120" s="3" t="inlineStr"/>
       <c r="D120" s="3" t="inlineStr"/>
-      <c r="E120" s="5" t="inlineStr">
+      <c r="E120" s="4" t="inlineStr">
         <is>
           <t>https://linkedin.com/in/alessandrolorizzo</t>
         </is>
@@ -6076,43 +5696,23 @@
       <c r="R121" s="3" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="inlineStr">
-        <is>
-          <t>Marina</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>Casasola</t>
-        </is>
-      </c>
+      <c r="A122" s="2" t="inlineStr"/>
+      <c r="B122" s="2" t="inlineStr"/>
       <c r="C122" s="2" t="inlineStr"/>
       <c r="D122" s="2" t="inlineStr"/>
-      <c r="E122" s="4" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/marinacasasola</t>
-        </is>
-      </c>
+      <c r="E122" s="2" t="inlineStr"/>
       <c r="F122" s="2" t="inlineStr">
         <is>
           <t>Be.Green Plant Design Italy</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr">
-        <is>
-          <t>AI-Enhanced Content Specialist | Digital Marketing, CRM &amp; Multi-Channel Content</t>
-        </is>
-      </c>
+      <c r="G122" s="2" t="inlineStr"/>
       <c r="H122" s="2" t="inlineStr">
         <is>
           <t>be.green</t>
         </is>
       </c>
-      <c r="I122" s="2" t="inlineStr">
-        <is>
-          <t>es</t>
-        </is>
-      </c>
+      <c r="I122" s="2" t="inlineStr"/>
       <c r="J122" s="2" t="inlineStr">
         <is>
           <t>30 Giorni</t>
@@ -6176,43 +5776,23 @@
       <c r="R123" s="2" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="3" t="inlineStr">
-        <is>
-          <t>Victoria</t>
-        </is>
-      </c>
-      <c r="B124" s="3" t="inlineStr">
-        <is>
-          <t>M.</t>
-        </is>
-      </c>
+      <c r="A124" s="3" t="inlineStr"/>
+      <c r="B124" s="3" t="inlineStr"/>
       <c r="C124" s="3" t="inlineStr"/>
       <c r="D124" s="3" t="inlineStr"/>
-      <c r="E124" s="5" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/vicment</t>
-        </is>
-      </c>
+      <c r="E124" s="3" t="inlineStr"/>
       <c r="F124" s="3" t="inlineStr">
         <is>
           <t>Bears with Benefits IT</t>
         </is>
       </c>
-      <c r="G124" s="3" t="inlineStr">
-        <is>
-          <t>Senior Affiliate Manager</t>
-        </is>
-      </c>
+      <c r="G124" s="3" t="inlineStr"/>
       <c r="H124" s="3" t="inlineStr">
         <is>
-          <t>bears-with-benefits.com</t>
-        </is>
-      </c>
-      <c r="I124" s="3" t="inlineStr">
-        <is>
-          <t>de</t>
-        </is>
-      </c>
+          <t>bears-with-benefits.it</t>
+        </is>
+      </c>
+      <c r="I124" s="3" t="inlineStr"/>
       <c r="J124" s="3" t="inlineStr">
         <is>
           <t>30 Giorni</t>
@@ -6248,43 +5828,23 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="3" t="inlineStr">
-        <is>
-          <t>Maximilian</t>
-        </is>
-      </c>
-      <c r="B125" s="3" t="inlineStr">
-        <is>
-          <t>Helmers</t>
-        </is>
-      </c>
+      <c r="A125" s="3" t="inlineStr"/>
+      <c r="B125" s="3" t="inlineStr"/>
       <c r="C125" s="3" t="inlineStr"/>
       <c r="D125" s="3" t="inlineStr"/>
-      <c r="E125" s="5" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/maximilian-helmers-501358209</t>
-        </is>
-      </c>
+      <c r="E125" s="3" t="inlineStr"/>
       <c r="F125" s="3" t="inlineStr">
         <is>
           <t>Bears with Benefits IT</t>
         </is>
       </c>
-      <c r="G125" s="3" t="inlineStr">
-        <is>
-          <t>Junior Affiliate Manager</t>
-        </is>
-      </c>
+      <c r="G125" s="3" t="inlineStr"/>
       <c r="H125" s="3" t="inlineStr">
         <is>
-          <t>bears-with-benefits.com</t>
-        </is>
-      </c>
-      <c r="I125" s="3" t="inlineStr">
-        <is>
-          <t>de</t>
-        </is>
-      </c>
+          <t>bears-with-benefits.it</t>
+        </is>
+      </c>
+      <c r="I125" s="3" t="inlineStr"/>
       <c r="J125" s="3" t="inlineStr"/>
       <c r="K125" s="3" t="inlineStr"/>
       <c r="L125" s="3" t="inlineStr"/>
@@ -6296,43 +5856,23 @@
       <c r="R125" s="3" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="inlineStr">
-        <is>
-          <t>Madeline</t>
-        </is>
-      </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>MA</t>
-        </is>
-      </c>
+      <c r="A126" s="2" t="inlineStr"/>
+      <c r="B126" s="2" t="inlineStr"/>
       <c r="C126" s="2" t="inlineStr"/>
       <c r="D126" s="2" t="inlineStr"/>
-      <c r="E126" s="4" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/gyokukinnma-406745249</t>
-        </is>
-      </c>
+      <c r="E126" s="2" t="inlineStr"/>
       <c r="F126" s="2" t="inlineStr">
         <is>
           <t>Beatbot IT</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr">
-        <is>
-          <t>Senior Affiliate Marketing Manager</t>
-        </is>
-      </c>
+      <c r="G126" s="2" t="inlineStr"/>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>beatbot.com</t>
-        </is>
-      </c>
-      <c r="I126" s="2" t="inlineStr">
-        <is>
-          <t>jp</t>
-        </is>
-      </c>
+          <t>it.beatbot.com</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr"/>
       <c r="J126" s="2" t="inlineStr">
         <is>
           <t>30 Giorni</t>
@@ -6381,7 +5921,7 @@
       <c r="G127" s="2" t="inlineStr"/>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>beatbot.com</t>
+          <t>it.beatbot.com</t>
         </is>
       </c>
       <c r="I127" s="2" t="inlineStr"/>
@@ -6632,43 +6172,23 @@
       <c r="R133" s="3" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="inlineStr">
-        <is>
-          <t>Enrico</t>
-        </is>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>Redaelli</t>
-        </is>
-      </c>
+      <c r="A134" s="2" t="inlineStr"/>
+      <c r="B134" s="2" t="inlineStr"/>
       <c r="C134" s="2" t="inlineStr"/>
       <c r="D134" s="2" t="inlineStr"/>
-      <c r="E134" s="4" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/enrico-redaelli-7b897740</t>
-        </is>
-      </c>
+      <c r="E134" s="2" t="inlineStr"/>
       <c r="F134" s="2" t="inlineStr">
         <is>
           <t>Bennet IT</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr">
-        <is>
-          <t>E-Commerce &amp; Digital Marketing Manager</t>
-        </is>
-      </c>
+      <c r="G134" s="2" t="inlineStr"/>
       <c r="H134" s="2" t="inlineStr">
         <is>
           <t>bennet.com</t>
         </is>
       </c>
-      <c r="I134" s="2" t="inlineStr">
-        <is>
-          <t>it</t>
-        </is>
-      </c>
+      <c r="I134" s="2" t="inlineStr"/>
       <c r="J134" s="2" t="inlineStr">
         <is>
           <t>30 Giorni</t>
@@ -6704,43 +6224,23 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="2" t="inlineStr">
-        <is>
-          <t>Luca</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>Grignaffini</t>
-        </is>
-      </c>
+      <c r="A135" s="2" t="inlineStr"/>
+      <c r="B135" s="2" t="inlineStr"/>
       <c r="C135" s="2" t="inlineStr"/>
       <c r="D135" s="2" t="inlineStr"/>
-      <c r="E135" s="4" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/lucagrignaffini</t>
-        </is>
-      </c>
+      <c r="E135" s="2" t="inlineStr"/>
       <c r="F135" s="2" t="inlineStr">
         <is>
           <t>Bennet IT</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr">
-        <is>
-          <t>Specialista in marketing digitale</t>
-        </is>
-      </c>
+      <c r="G135" s="2" t="inlineStr"/>
       <c r="H135" s="2" t="inlineStr">
         <is>
           <t>bennet.com</t>
         </is>
       </c>
-      <c r="I135" s="2" t="inlineStr">
-        <is>
-          <t>it</t>
-        </is>
-      </c>
+      <c r="I135" s="2" t="inlineStr"/>
       <c r="J135" s="2" t="inlineStr"/>
       <c r="K135" s="2" t="inlineStr"/>
       <c r="L135" s="2" t="inlineStr"/>
@@ -7628,43 +7128,23 @@
       <c r="R157" s="3" t="inlineStr"/>
     </row>
     <row r="158">
-      <c r="A158" s="2" t="inlineStr">
-        <is>
-          <t>Emily</t>
-        </is>
-      </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>Crosby</t>
-        </is>
-      </c>
+      <c r="A158" s="2" t="inlineStr"/>
+      <c r="B158" s="2" t="inlineStr"/>
       <c r="C158" s="2" t="inlineStr"/>
       <c r="D158" s="2" t="inlineStr"/>
-      <c r="E158" s="4" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/emily-crosby-creativelead</t>
-        </is>
-      </c>
+      <c r="E158" s="2" t="inlineStr"/>
       <c r="F158" s="2" t="inlineStr">
         <is>
           <t>Blizzard Gear Store IT</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr">
-        <is>
-          <t>Digital Marketing Manager - Diablo</t>
-        </is>
-      </c>
+      <c r="G158" s="2" t="inlineStr"/>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>blizzard.com</t>
-        </is>
-      </c>
-      <c r="I158" s="2" t="inlineStr">
-        <is>
-          <t>us</t>
-        </is>
-      </c>
+          <t>eu.gear.blizzard.com</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="inlineStr"/>
       <c r="J158" s="2" t="inlineStr">
         <is>
           <t>30 Giorni</t>
@@ -7700,43 +7180,23 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="inlineStr">
-        <is>
-          <t>Britain</t>
-        </is>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>Taylor</t>
-        </is>
-      </c>
+      <c r="A159" s="2" t="inlineStr"/>
+      <c r="B159" s="2" t="inlineStr"/>
       <c r="C159" s="2" t="inlineStr"/>
       <c r="D159" s="2" t="inlineStr"/>
-      <c r="E159" s="4" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/britain-taylor</t>
-        </is>
-      </c>
+      <c r="E159" s="2" t="inlineStr"/>
       <c r="F159" s="2" t="inlineStr">
         <is>
           <t>Blizzard Gear Store IT</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr">
-        <is>
-          <t>Sr. Manager, Digital Marketing</t>
-        </is>
-      </c>
+      <c r="G159" s="2" t="inlineStr"/>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t>blizzard.com</t>
-        </is>
-      </c>
-      <c r="I159" s="2" t="inlineStr">
-        <is>
-          <t>us</t>
-        </is>
-      </c>
+          <t>eu.gear.blizzard.com</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr"/>
       <c r="J159" s="2" t="inlineStr"/>
       <c r="K159" s="2" t="inlineStr"/>
       <c r="L159" s="2" t="inlineStr"/>
@@ -7920,7 +7380,7 @@
       </c>
       <c r="C164" s="3" t="inlineStr"/>
       <c r="D164" s="3" t="inlineStr"/>
-      <c r="E164" s="5" t="inlineStr">
+      <c r="E164" s="4" t="inlineStr">
         <is>
           <t>https://linkedin.com/in/jonas-sebastian-schmidt</t>
         </is>
@@ -7992,7 +7452,7 @@
       </c>
       <c r="C165" s="3" t="inlineStr"/>
       <c r="D165" s="3" t="inlineStr"/>
-      <c r="E165" s="5" t="inlineStr">
+      <c r="E165" s="4" t="inlineStr">
         <is>
           <t>https://linkedin.com/in/kalle-himmelein-975037269</t>
         </is>
@@ -8204,7 +7664,7 @@
       </c>
       <c r="C170" s="2" t="inlineStr"/>
       <c r="D170" s="2" t="inlineStr"/>
-      <c r="E170" s="4" t="inlineStr">
+      <c r="E170" s="5" t="inlineStr">
         <is>
           <t>https://linkedin.com/in/davide-garofalo-377649188</t>
         </is>
@@ -8266,17 +7726,17 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>📈</t>
+          <t>Giuliano</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>Giuliano Ciccarese</t>
+          <t>Ciccarese</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr"/>
       <c r="D171" s="2" t="inlineStr"/>
-      <c r="E171" s="4" t="inlineStr">
+      <c r="E171" s="5" t="inlineStr">
         <is>
           <t>https://linkedin.com/in/ciccarese</t>
         </is>
@@ -8392,43 +7852,23 @@
       <c r="R173" s="3" t="inlineStr"/>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="inlineStr">
-        <is>
-          <t>Claudia</t>
-        </is>
-      </c>
-      <c r="B174" s="2" t="inlineStr">
-        <is>
-          <t>Sogus</t>
-        </is>
-      </c>
+      <c r="A174" s="2" t="inlineStr"/>
+      <c r="B174" s="2" t="inlineStr"/>
       <c r="C174" s="2" t="inlineStr"/>
       <c r="D174" s="2" t="inlineStr"/>
-      <c r="E174" s="4" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/claudia-sogus-27038b32</t>
-        </is>
-      </c>
+      <c r="E174" s="2" t="inlineStr"/>
       <c r="F174" s="2" t="inlineStr">
         <is>
           <t>Boggi IT</t>
         </is>
       </c>
-      <c r="G174" s="2" t="inlineStr">
-        <is>
-          <t>Head of eCommerce &amp; Digital Marketing</t>
-        </is>
-      </c>
+      <c r="G174" s="2" t="inlineStr"/>
       <c r="H174" s="2" t="inlineStr">
         <is>
           <t>boggi.com</t>
         </is>
       </c>
-      <c r="I174" s="2" t="inlineStr">
-        <is>
-          <t>it</t>
-        </is>
-      </c>
+      <c r="I174" s="2" t="inlineStr"/>
       <c r="J174" s="2" t="inlineStr">
         <is>
           <t>30 Giorni</t>
@@ -8464,43 +7904,23 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="inlineStr">
-        <is>
-          <t>Lara</t>
-        </is>
-      </c>
-      <c r="B175" s="2" t="inlineStr">
-        <is>
-          <t>Convertino</t>
-        </is>
-      </c>
+      <c r="A175" s="2" t="inlineStr"/>
+      <c r="B175" s="2" t="inlineStr"/>
       <c r="C175" s="2" t="inlineStr"/>
       <c r="D175" s="2" t="inlineStr"/>
-      <c r="E175" s="4" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/lara-convertino</t>
-        </is>
-      </c>
+      <c r="E175" s="2" t="inlineStr"/>
       <c r="F175" s="2" t="inlineStr">
         <is>
           <t>Boggi IT</t>
         </is>
       </c>
-      <c r="G175" s="2" t="inlineStr">
-        <is>
-          <t>Digital Marketplace Specialist</t>
-        </is>
-      </c>
+      <c r="G175" s="2" t="inlineStr"/>
       <c r="H175" s="2" t="inlineStr">
         <is>
           <t>boggi.com</t>
         </is>
       </c>
-      <c r="I175" s="2" t="inlineStr">
-        <is>
-          <t>it</t>
-        </is>
-      </c>
+      <c r="I175" s="2" t="inlineStr"/>
       <c r="J175" s="2" t="inlineStr"/>
       <c r="K175" s="2" t="inlineStr"/>
       <c r="L175" s="2" t="inlineStr"/>
@@ -8673,43 +8093,23 @@
       <c r="R179" s="2" t="inlineStr"/>
     </row>
     <row r="180">
-      <c r="A180" s="3" t="inlineStr">
-        <is>
-          <t>Eniko</t>
-        </is>
-      </c>
-      <c r="B180" s="3" t="inlineStr">
-        <is>
-          <t>Beres-Deak</t>
-        </is>
-      </c>
+      <c r="A180" s="3" t="inlineStr"/>
+      <c r="B180" s="3" t="inlineStr"/>
       <c r="C180" s="3" t="inlineStr"/>
       <c r="D180" s="3" t="inlineStr"/>
-      <c r="E180" s="5" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/eniko-beres-deak-97a7591a8</t>
-        </is>
-      </c>
+      <c r="E180" s="3" t="inlineStr"/>
       <c r="F180" s="3" t="inlineStr">
         <is>
           <t>Boohoo.com IT</t>
         </is>
       </c>
-      <c r="G180" s="3" t="inlineStr">
-        <is>
-          <t>Senior Affiliate Marketing Executive</t>
-        </is>
-      </c>
+      <c r="G180" s="3" t="inlineStr"/>
       <c r="H180" s="3" t="inlineStr">
         <is>
-          <t>boohoo.com</t>
-        </is>
-      </c>
-      <c r="I180" s="3" t="inlineStr">
-        <is>
-          <t>gb</t>
-        </is>
-      </c>
+          <t>eu.boohoo.com</t>
+        </is>
+      </c>
+      <c r="I180" s="3" t="inlineStr"/>
       <c r="J180" s="3" t="inlineStr">
         <is>
           <t>30 Giorni</t>
@@ -8758,7 +8158,7 @@
       <c r="G181" s="3" t="inlineStr"/>
       <c r="H181" s="3" t="inlineStr">
         <is>
-          <t>boohoo.com</t>
+          <t>eu.boohoo.com</t>
         </is>
       </c>
       <c r="I181" s="3" t="inlineStr"/>
@@ -9009,43 +8409,23 @@
       <c r="R187" s="2" t="inlineStr"/>
     </row>
     <row r="188">
-      <c r="A188" s="3" t="inlineStr">
-        <is>
-          <t>Elenia</t>
-        </is>
-      </c>
-      <c r="B188" s="3" t="inlineStr">
-        <is>
-          <t>Masoero</t>
-        </is>
-      </c>
+      <c r="A188" s="3" t="inlineStr"/>
+      <c r="B188" s="3" t="inlineStr"/>
       <c r="C188" s="3" t="inlineStr"/>
       <c r="D188" s="3" t="inlineStr"/>
-      <c r="E188" s="5" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/elenia-masoero-74772330</t>
-        </is>
-      </c>
+      <c r="E188" s="3" t="inlineStr"/>
       <c r="F188" s="3" t="inlineStr">
         <is>
           <t>Bottega Verde 2018 IT</t>
         </is>
       </c>
-      <c r="G188" s="3" t="inlineStr">
-        <is>
-          <t>Affiliate Marketing Manager</t>
-        </is>
-      </c>
+      <c r="G188" s="3" t="inlineStr"/>
       <c r="H188" s="3" t="inlineStr">
         <is>
-          <t>bottegaverde.com</t>
-        </is>
-      </c>
-      <c r="I188" s="3" t="inlineStr">
-        <is>
-          <t>it</t>
-        </is>
-      </c>
+          <t>bottegaverde.it</t>
+        </is>
+      </c>
+      <c r="I188" s="3" t="inlineStr"/>
       <c r="J188" s="3" t="inlineStr">
         <is>
           <t>30 Giorni</t>
@@ -9085,43 +8465,23 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="3" t="inlineStr">
-        <is>
-          <t>Edoardo</t>
-        </is>
-      </c>
-      <c r="B189" s="3" t="inlineStr">
-        <is>
-          <t>Novarese ✓</t>
-        </is>
-      </c>
+      <c r="A189" s="3" t="inlineStr"/>
+      <c r="B189" s="3" t="inlineStr"/>
       <c r="C189" s="3" t="inlineStr"/>
       <c r="D189" s="3" t="inlineStr"/>
-      <c r="E189" s="5" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/edoardo-novarese-✓-722b6885</t>
-        </is>
-      </c>
+      <c r="E189" s="3" t="inlineStr"/>
       <c r="F189" s="3" t="inlineStr">
         <is>
           <t>Bottega Verde 2018 IT</t>
         </is>
       </c>
-      <c r="G189" s="3" t="inlineStr">
-        <is>
-          <t>Digital Marketing Performance Manager</t>
-        </is>
-      </c>
+      <c r="G189" s="3" t="inlineStr"/>
       <c r="H189" s="3" t="inlineStr">
         <is>
-          <t>bottegaverde.com</t>
-        </is>
-      </c>
-      <c r="I189" s="3" t="inlineStr">
-        <is>
-          <t>it</t>
-        </is>
-      </c>
+          <t>bottegaverde.it</t>
+        </is>
+      </c>
+      <c r="I189" s="3" t="inlineStr"/>
       <c r="J189" s="3" t="inlineStr"/>
       <c r="K189" s="3" t="inlineStr"/>
       <c r="L189" s="3" t="inlineStr"/>
@@ -9213,43 +8573,23 @@
       <c r="R191" s="2" t="inlineStr"/>
     </row>
     <row r="192">
-      <c r="A192" s="3" t="inlineStr">
-        <is>
-          <t>Martina</t>
-        </is>
-      </c>
-      <c r="B192" s="3" t="inlineStr">
-        <is>
-          <t>Cocco</t>
-        </is>
-      </c>
+      <c r="A192" s="3" t="inlineStr"/>
+      <c r="B192" s="3" t="inlineStr"/>
       <c r="C192" s="3" t="inlineStr"/>
       <c r="D192" s="3" t="inlineStr"/>
-      <c r="E192" s="5" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/martinacocco</t>
-        </is>
-      </c>
+      <c r="E192" s="3" t="inlineStr"/>
       <c r="F192" s="3" t="inlineStr">
         <is>
           <t>BricoBravo IT</t>
         </is>
       </c>
-      <c r="G192" s="3" t="inlineStr">
-        <is>
-          <t>Head of Digital Marketing</t>
-        </is>
-      </c>
+      <c r="G192" s="3" t="inlineStr"/>
       <c r="H192" s="3" t="inlineStr">
         <is>
           <t>bricobravo.com</t>
         </is>
       </c>
-      <c r="I192" s="3" t="inlineStr">
-        <is>
-          <t>it</t>
-        </is>
-      </c>
+      <c r="I192" s="3" t="inlineStr"/>
       <c r="J192" s="3" t="inlineStr">
         <is>
           <t>20 Giorni</t>
@@ -9285,43 +8625,23 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="3" t="inlineStr">
-        <is>
-          <t>Federico</t>
-        </is>
-      </c>
-      <c r="B193" s="3" t="inlineStr">
-        <is>
-          <t>Samà</t>
-        </is>
-      </c>
+      <c r="A193" s="3" t="inlineStr"/>
+      <c r="B193" s="3" t="inlineStr"/>
       <c r="C193" s="3" t="inlineStr"/>
       <c r="D193" s="3" t="inlineStr"/>
-      <c r="E193" s="5" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/federico-samà-182625129</t>
-        </is>
-      </c>
+      <c r="E193" s="3" t="inlineStr"/>
       <c r="F193" s="3" t="inlineStr">
         <is>
           <t>BricoBravo IT</t>
         </is>
       </c>
-      <c r="G193" s="3" t="inlineStr">
-        <is>
-          <t>E-commerce &amp; Digital Marketing campaign manager</t>
-        </is>
-      </c>
+      <c r="G193" s="3" t="inlineStr"/>
       <c r="H193" s="3" t="inlineStr">
         <is>
           <t>bricobravo.com</t>
         </is>
       </c>
-      <c r="I193" s="3" t="inlineStr">
-        <is>
-          <t>it</t>
-        </is>
-      </c>
+      <c r="I193" s="3" t="inlineStr"/>
       <c r="J193" s="3" t="inlineStr"/>
       <c r="K193" s="3" t="inlineStr"/>
       <c r="L193" s="3" t="inlineStr"/>
@@ -9577,7 +8897,7 @@
       </c>
       <c r="C200" s="3" t="inlineStr"/>
       <c r="D200" s="3" t="inlineStr"/>
-      <c r="E200" s="5" t="inlineStr">
+      <c r="E200" s="4" t="inlineStr">
         <is>
           <t>https://linkedin.com/in/michael-dorsch-a4396b24a</t>
         </is>
@@ -9649,7 +8969,7 @@
       </c>
       <c r="C201" s="3" t="inlineStr"/>
       <c r="D201" s="3" t="inlineStr"/>
-      <c r="E201" s="5" t="inlineStr">
+      <c r="E201" s="4" t="inlineStr">
         <is>
           <t>https://linkedin.com/in/aniko-fischer</t>
         </is>
@@ -9761,43 +9081,23 @@
       <c r="R203" s="2" t="inlineStr"/>
     </row>
     <row r="204">
-      <c r="A204" s="3" t="inlineStr">
-        <is>
-          <t>Sara</t>
-        </is>
-      </c>
-      <c r="B204" s="3" t="inlineStr">
-        <is>
-          <t>Rojas</t>
-        </is>
-      </c>
+      <c r="A204" s="3" t="inlineStr"/>
+      <c r="B204" s="3" t="inlineStr"/>
       <c r="C204" s="3" t="inlineStr"/>
       <c r="D204" s="3" t="inlineStr"/>
-      <c r="E204" s="5" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/sara-rojas-5172539</t>
-        </is>
-      </c>
+      <c r="E204" s="3" t="inlineStr"/>
       <c r="F204" s="3" t="inlineStr">
         <is>
           <t>Bulk IT</t>
         </is>
       </c>
-      <c r="G204" s="3" t="inlineStr">
-        <is>
-          <t>E-commerce Digital Marketing / Trading Executive</t>
-        </is>
-      </c>
+      <c r="G204" s="3" t="inlineStr"/>
       <c r="H204" s="3" t="inlineStr">
         <is>
           <t>bulk.com</t>
         </is>
       </c>
-      <c r="I204" s="3" t="inlineStr">
-        <is>
-          <t>gb</t>
-        </is>
-      </c>
+      <c r="I204" s="3" t="inlineStr"/>
       <c r="J204" s="3" t="inlineStr">
         <is>
           <t>30 Giorni</t>
@@ -9833,43 +9133,23 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="3" t="inlineStr">
-        <is>
-          <t>Luke</t>
-        </is>
-      </c>
-      <c r="B205" s="3" t="inlineStr">
-        <is>
-          <t>Morris-Timms</t>
-        </is>
-      </c>
+      <c r="A205" s="3" t="inlineStr"/>
+      <c r="B205" s="3" t="inlineStr"/>
       <c r="C205" s="3" t="inlineStr"/>
       <c r="D205" s="3" t="inlineStr"/>
-      <c r="E205" s="5" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/luke-morris-timms-835b50140</t>
-        </is>
-      </c>
+      <c r="E205" s="3" t="inlineStr"/>
       <c r="F205" s="3" t="inlineStr">
         <is>
           <t>Bulk IT</t>
         </is>
       </c>
-      <c r="G205" s="3" t="inlineStr">
-        <is>
-          <t>Junior Digital Marketing Assistant</t>
-        </is>
-      </c>
+      <c r="G205" s="3" t="inlineStr"/>
       <c r="H205" s="3" t="inlineStr">
         <is>
           <t>bulk.com</t>
         </is>
       </c>
-      <c r="I205" s="3" t="inlineStr">
-        <is>
-          <t>gb</t>
-        </is>
-      </c>
+      <c r="I205" s="3" t="inlineStr"/>
       <c r="J205" s="3" t="inlineStr"/>
       <c r="K205" s="3" t="inlineStr"/>
       <c r="L205" s="3" t="inlineStr"/>
@@ -10041,43 +9321,23 @@
       <c r="R209" s="3" t="inlineStr"/>
     </row>
     <row r="210">
-      <c r="A210" s="2" t="inlineStr">
-        <is>
-          <t>Milena</t>
-        </is>
-      </c>
-      <c r="B210" s="2" t="inlineStr">
-        <is>
-          <t>Kozaczuk</t>
-        </is>
-      </c>
+      <c r="A210" s="2" t="inlineStr"/>
+      <c r="B210" s="2" t="inlineStr"/>
       <c r="C210" s="2" t="inlineStr"/>
       <c r="D210" s="2" t="inlineStr"/>
-      <c r="E210" s="4" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/milenakozaczuk</t>
-        </is>
-      </c>
+      <c r="E210" s="2" t="inlineStr"/>
       <c r="F210" s="2" t="inlineStr">
         <is>
           <t>Calzedonia IT</t>
         </is>
       </c>
-      <c r="G210" s="2" t="inlineStr">
-        <is>
-          <t>Junior Ecommerce &amp; Digital Marketing Specialist</t>
-        </is>
-      </c>
+      <c r="G210" s="2" t="inlineStr"/>
       <c r="H210" s="2" t="inlineStr">
         <is>
           <t>calzedonia.com</t>
         </is>
       </c>
-      <c r="I210" s="2" t="inlineStr">
-        <is>
-          <t>pl</t>
-        </is>
-      </c>
+      <c r="I210" s="2" t="inlineStr"/>
       <c r="J210" s="2" t="inlineStr">
         <is>
           <t>30 Giorni</t>
@@ -10461,43 +9721,23 @@
       <c r="R219" s="2" t="inlineStr"/>
     </row>
     <row r="220">
-      <c r="A220" s="3" t="inlineStr">
-        <is>
-          <t>Giulia</t>
-        </is>
-      </c>
-      <c r="B220" s="3" t="inlineStr">
-        <is>
-          <t>Piccinelli</t>
-        </is>
-      </c>
+      <c r="A220" s="3" t="inlineStr"/>
+      <c r="B220" s="3" t="inlineStr"/>
       <c r="C220" s="3" t="inlineStr"/>
       <c r="D220" s="3" t="inlineStr"/>
-      <c r="E220" s="5" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/giulia-piccinelli</t>
-        </is>
-      </c>
+      <c r="E220" s="3" t="inlineStr"/>
       <c r="F220" s="3" t="inlineStr">
         <is>
           <t>Capellopoint IT</t>
         </is>
       </c>
-      <c r="G220" s="3" t="inlineStr">
-        <is>
-          <t>Digital Marketing Specialist</t>
-        </is>
-      </c>
+      <c r="G220" s="3" t="inlineStr"/>
       <c r="H220" s="3" t="inlineStr">
         <is>
           <t>capellopoint.it</t>
         </is>
       </c>
-      <c r="I220" s="3" t="inlineStr">
-        <is>
-          <t>it</t>
-        </is>
-      </c>
+      <c r="I220" s="3" t="inlineStr"/>
       <c r="J220" s="3" t="inlineStr">
         <is>
           <t>30 Giorni</t>
@@ -10725,43 +9965,23 @@
       <c r="R225" s="3" t="inlineStr"/>
     </row>
     <row r="226">
-      <c r="A226" s="2" t="inlineStr">
-        <is>
-          <t>Jonas</t>
-        </is>
-      </c>
-      <c r="B226" s="2" t="inlineStr">
-        <is>
-          <t>Lapinas</t>
-        </is>
-      </c>
+      <c r="A226" s="2" t="inlineStr"/>
+      <c r="B226" s="2" t="inlineStr"/>
       <c r="C226" s="2" t="inlineStr"/>
       <c r="D226" s="2" t="inlineStr"/>
-      <c r="E226" s="4" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/jonas-lapinas-a57042a4</t>
-        </is>
-      </c>
+      <c r="E226" s="2" t="inlineStr"/>
       <c r="F226" s="2" t="inlineStr">
         <is>
           <t>carVertical IT</t>
         </is>
       </c>
-      <c r="G226" s="2" t="inlineStr">
-        <is>
-          <t>Affiliate Marketing Manager</t>
-        </is>
-      </c>
+      <c r="G226" s="2" t="inlineStr"/>
       <c r="H226" s="2" t="inlineStr">
         <is>
           <t>carvertical.com</t>
         </is>
       </c>
-      <c r="I226" s="2" t="inlineStr">
-        <is>
-          <t>lt</t>
-        </is>
-      </c>
+      <c r="I226" s="2" t="inlineStr"/>
       <c r="J226" s="2" t="inlineStr">
         <is>
           <t>30 Giorni</t>
@@ -10797,43 +10017,23 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="2" t="inlineStr">
-        <is>
-          <t>Dominyka</t>
-        </is>
-      </c>
-      <c r="B227" s="2" t="inlineStr">
-        <is>
-          <t>Kurklietytė-Jocė</t>
-        </is>
-      </c>
+      <c r="A227" s="2" t="inlineStr"/>
+      <c r="B227" s="2" t="inlineStr"/>
       <c r="C227" s="2" t="inlineStr"/>
       <c r="D227" s="2" t="inlineStr"/>
-      <c r="E227" s="4" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/dominyka-kurklietyte</t>
-        </is>
-      </c>
+      <c r="E227" s="2" t="inlineStr"/>
       <c r="F227" s="2" t="inlineStr">
         <is>
           <t>carVertical IT</t>
         </is>
       </c>
-      <c r="G227" s="2" t="inlineStr">
-        <is>
-          <t>Affiliate Marketing Manager</t>
-        </is>
-      </c>
+      <c r="G227" s="2" t="inlineStr"/>
       <c r="H227" s="2" t="inlineStr">
         <is>
           <t>carvertical.com</t>
         </is>
       </c>
-      <c r="I227" s="2" t="inlineStr">
-        <is>
-          <t>lt</t>
-        </is>
-      </c>
+      <c r="I227" s="2" t="inlineStr"/>
       <c r="J227" s="2" t="inlineStr"/>
       <c r="K227" s="2" t="inlineStr"/>
       <c r="L227" s="2" t="inlineStr"/>
@@ -10845,43 +10045,23 @@
       <c r="R227" s="2" t="inlineStr"/>
     </row>
     <row r="228">
-      <c r="A228" s="3" t="inlineStr">
-        <is>
-          <t>Gabriele</t>
-        </is>
-      </c>
-      <c r="B228" s="3" t="inlineStr">
-        <is>
-          <t>Frassanito</t>
-        </is>
-      </c>
+      <c r="A228" s="3" t="inlineStr"/>
+      <c r="B228" s="3" t="inlineStr"/>
       <c r="C228" s="3" t="inlineStr"/>
       <c r="D228" s="3" t="inlineStr"/>
-      <c r="E228" s="5" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/gabriele-frassanito-119b43211</t>
-        </is>
-      </c>
+      <c r="E228" s="3" t="inlineStr"/>
       <c r="F228" s="3" t="inlineStr">
         <is>
           <t>Casa39 IT</t>
         </is>
       </c>
-      <c r="G228" s="3" t="inlineStr">
-        <is>
-          <t>Digital Marketing Manager</t>
-        </is>
-      </c>
+      <c r="G228" s="3" t="inlineStr"/>
       <c r="H228" s="3" t="inlineStr">
         <is>
           <t>casa39.it</t>
         </is>
       </c>
-      <c r="I228" s="3" t="inlineStr">
-        <is>
-          <t>it</t>
-        </is>
-      </c>
+      <c r="I228" s="3" t="inlineStr"/>
       <c r="J228" s="3" t="inlineStr">
         <is>
           <t>30 Giorni</t>
@@ -10921,43 +10101,23 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="3" t="inlineStr">
-        <is>
-          <t>Diego</t>
-        </is>
-      </c>
-      <c r="B229" s="3" t="inlineStr">
-        <is>
-          <t>Palma</t>
-        </is>
-      </c>
+      <c r="A229" s="3" t="inlineStr"/>
+      <c r="B229" s="3" t="inlineStr"/>
       <c r="C229" s="3" t="inlineStr"/>
       <c r="D229" s="3" t="inlineStr"/>
-      <c r="E229" s="5" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/diego-palma-1361a0195</t>
-        </is>
-      </c>
+      <c r="E229" s="3" t="inlineStr"/>
       <c r="F229" s="3" t="inlineStr">
         <is>
           <t>Casa39 IT</t>
         </is>
       </c>
-      <c r="G229" s="3" t="inlineStr">
-        <is>
-          <t>Esperto in digital marketing e comunicazione</t>
-        </is>
-      </c>
+      <c r="G229" s="3" t="inlineStr"/>
       <c r="H229" s="3" t="inlineStr">
         <is>
           <t>casa39.it</t>
         </is>
       </c>
-      <c r="I229" s="3" t="inlineStr">
-        <is>
-          <t>it</t>
-        </is>
-      </c>
+      <c r="I229" s="3" t="inlineStr"/>
       <c r="J229" s="3" t="inlineStr"/>
       <c r="K229" s="3" t="inlineStr"/>
       <c r="L229" s="3" t="inlineStr"/>
@@ -11145,7 +10305,7 @@
       </c>
       <c r="C234" s="2" t="inlineStr"/>
       <c r="D234" s="2" t="inlineStr"/>
-      <c r="E234" s="4" t="inlineStr">
+      <c r="E234" s="5" t="inlineStr">
         <is>
           <t>https://linkedin.com/in/victoria-balduino</t>
         </is>
@@ -11233,43 +10393,23 @@
       <c r="R235" s="2" t="inlineStr"/>
     </row>
     <row r="236">
-      <c r="A236" s="3" t="inlineStr">
-        <is>
-          <t>Baptiste</t>
-        </is>
-      </c>
-      <c r="B236" s="3" t="inlineStr">
-        <is>
-          <t>D.</t>
-        </is>
-      </c>
+      <c r="A236" s="3" t="inlineStr"/>
+      <c r="B236" s="3" t="inlineStr"/>
       <c r="C236" s="3" t="inlineStr"/>
       <c r="D236" s="3" t="inlineStr"/>
-      <c r="E236" s="5" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/baptiste-dc</t>
-        </is>
-      </c>
+      <c r="E236" s="3" t="inlineStr"/>
       <c r="F236" s="3" t="inlineStr">
         <is>
           <t>Cheerz IT</t>
         </is>
       </c>
-      <c r="G236" s="3" t="inlineStr">
-        <is>
-          <t>SEO &amp; Affiliate Manager</t>
-        </is>
-      </c>
+      <c r="G236" s="3" t="inlineStr"/>
       <c r="H236" s="3" t="inlineStr">
         <is>
           <t>cheerz.com</t>
         </is>
       </c>
-      <c r="I236" s="3" t="inlineStr">
-        <is>
-          <t>fr</t>
-        </is>
-      </c>
+      <c r="I236" s="3" t="inlineStr"/>
       <c r="J236" s="3" t="inlineStr">
         <is>
           <t>30 Giorni</t>
@@ -11493,43 +10633,23 @@
       <c r="R241" s="3" t="inlineStr"/>
     </row>
     <row r="242">
-      <c r="A242" s="2" t="inlineStr">
-        <is>
-          <t>Matteo</t>
-        </is>
-      </c>
-      <c r="B242" s="2" t="inlineStr">
-        <is>
-          <t>Favini</t>
-        </is>
-      </c>
+      <c r="A242" s="2" t="inlineStr"/>
+      <c r="B242" s="2" t="inlineStr"/>
       <c r="C242" s="2" t="inlineStr"/>
       <c r="D242" s="2" t="inlineStr"/>
-      <c r="E242" s="4" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/matteo-favini</t>
-        </is>
-      </c>
+      <c r="E242" s="2" t="inlineStr"/>
       <c r="F242" s="2" t="inlineStr">
         <is>
           <t>Cisalfa Sport IT</t>
         </is>
       </c>
-      <c r="G242" s="2" t="inlineStr">
-        <is>
-          <t>Digital Marketing Specialist</t>
-        </is>
-      </c>
+      <c r="G242" s="2" t="inlineStr"/>
       <c r="H242" s="2" t="inlineStr">
         <is>
           <t>cisalfasport.it</t>
         </is>
       </c>
-      <c r="I242" s="2" t="inlineStr">
-        <is>
-          <t>it</t>
-        </is>
-      </c>
+      <c r="I242" s="2" t="inlineStr"/>
       <c r="J242" s="2" t="inlineStr">
         <is>
           <t>30 Giorni</t>
@@ -11833,43 +10953,23 @@
       <c r="R249" s="3" t="inlineStr"/>
     </row>
     <row r="250">
-      <c r="A250" s="2" t="inlineStr">
-        <is>
-          <t>Cocopac</t>
-        </is>
-      </c>
-      <c r="B250" s="2" t="inlineStr">
-        <is>
-          <t>Cocopac</t>
-        </is>
-      </c>
+      <c r="A250" s="2" t="inlineStr"/>
+      <c r="B250" s="2" t="inlineStr"/>
       <c r="C250" s="2" t="inlineStr"/>
       <c r="D250" s="2" t="inlineStr"/>
-      <c r="E250" s="4" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/cocopac-cocopac-1b3589230</t>
-        </is>
-      </c>
+      <c r="E250" s="2" t="inlineStr"/>
       <c r="F250" s="2" t="inlineStr">
         <is>
           <t>Cocunat IT</t>
         </is>
       </c>
-      <c r="G250" s="2" t="inlineStr">
-        <is>
-          <t>Responsable marketing numérique</t>
-        </is>
-      </c>
+      <c r="G250" s="2" t="inlineStr"/>
       <c r="H250" s="2" t="inlineStr">
         <is>
           <t>cocunat.com</t>
         </is>
       </c>
-      <c r="I250" s="2" t="inlineStr">
-        <is>
-          <t>es</t>
-        </is>
-      </c>
+      <c r="I250" s="2" t="inlineStr"/>
       <c r="J250" s="2" t="inlineStr">
         <is>
           <t>30 Giorni</t>
@@ -12327,43 +11427,23 @@
       <c r="R261" s="3" t="inlineStr"/>
     </row>
     <row r="262">
-      <c r="A262" s="2" t="inlineStr">
-        <is>
-          <t>Tiziano</t>
-        </is>
-      </c>
-      <c r="B262" s="2" t="inlineStr">
-        <is>
-          <t>Carozza</t>
-        </is>
-      </c>
+      <c r="A262" s="2" t="inlineStr"/>
+      <c r="B262" s="2" t="inlineStr"/>
       <c r="C262" s="2" t="inlineStr"/>
       <c r="D262" s="2" t="inlineStr"/>
-      <c r="E262" s="4" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/tizianocarozza</t>
-        </is>
-      </c>
+      <c r="E262" s="2" t="inlineStr"/>
       <c r="F262" s="2" t="inlineStr">
         <is>
           <t>Corsi.it IT</t>
         </is>
       </c>
-      <c r="G262" s="2" t="inlineStr">
-        <is>
-          <t>Performance Marketing Specialist</t>
-        </is>
-      </c>
+      <c r="G262" s="2" t="inlineStr"/>
       <c r="H262" s="2" t="inlineStr">
         <is>
           <t>corsi.it</t>
         </is>
       </c>
-      <c r="I262" s="2" t="inlineStr">
-        <is>
-          <t>it</t>
-        </is>
-      </c>
+      <c r="I262" s="2" t="inlineStr"/>
       <c r="J262" s="2" t="inlineStr">
         <is>
           <t>30 Giorni</t>
@@ -12399,43 +11479,23 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="2" t="inlineStr">
-        <is>
-          <t>Federico</t>
-        </is>
-      </c>
-      <c r="B263" s="2" t="inlineStr">
-        <is>
-          <t>Pullarà</t>
-        </is>
-      </c>
+      <c r="A263" s="2" t="inlineStr"/>
+      <c r="B263" s="2" t="inlineStr"/>
       <c r="C263" s="2" t="inlineStr"/>
       <c r="D263" s="2" t="inlineStr"/>
-      <c r="E263" s="4" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/mdrzn</t>
-        </is>
-      </c>
+      <c r="E263" s="2" t="inlineStr"/>
       <c r="F263" s="2" t="inlineStr">
         <is>
           <t>Corsi.it IT</t>
         </is>
       </c>
-      <c r="G263" s="2" t="inlineStr">
-        <is>
-          <t>Specialista in marketing digitale</t>
-        </is>
-      </c>
+      <c r="G263" s="2" t="inlineStr"/>
       <c r="H263" s="2" t="inlineStr">
         <is>
           <t>corsi.it</t>
         </is>
       </c>
-      <c r="I263" s="2" t="inlineStr">
-        <is>
-          <t>it</t>
-        </is>
-      </c>
+      <c r="I263" s="2" t="inlineStr"/>
       <c r="J263" s="2" t="inlineStr"/>
       <c r="K263" s="2" t="inlineStr"/>
       <c r="L263" s="2" t="inlineStr"/>
@@ -12603,43 +11663,23 @@
       <c r="R267" s="2" t="inlineStr"/>
     </row>
     <row r="268">
-      <c r="A268" s="3" t="inlineStr">
-        <is>
-          <t>Cintia</t>
-        </is>
-      </c>
-      <c r="B268" s="3" t="inlineStr">
-        <is>
-          <t>Carlotti</t>
-        </is>
-      </c>
+      <c r="A268" s="3" t="inlineStr"/>
+      <c r="B268" s="3" t="inlineStr"/>
       <c r="C268" s="3" t="inlineStr"/>
       <c r="D268" s="3" t="inlineStr"/>
-      <c r="E268" s="5" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/cintia-carlotti-1b92a535</t>
-        </is>
-      </c>
+      <c r="E268" s="3" t="inlineStr"/>
       <c r="F268" s="3" t="inlineStr">
         <is>
           <t>Costa Crociere IT</t>
         </is>
       </c>
-      <c r="G268" s="3" t="inlineStr">
-        <is>
-          <t>Head of Digital Marketing - Americas</t>
-        </is>
-      </c>
+      <c r="G268" s="3" t="inlineStr"/>
       <c r="H268" s="3" t="inlineStr">
         <is>
           <t>costacrociere.it</t>
         </is>
       </c>
-      <c r="I268" s="3" t="inlineStr">
-        <is>
-          <t>br</t>
-        </is>
-      </c>
+      <c r="I268" s="3" t="inlineStr"/>
       <c r="J268" s="3" t="inlineStr">
         <is>
           <t>30 Giorni</t>
@@ -12675,43 +11715,23 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="3" t="inlineStr">
-        <is>
-          <t>Ana</t>
-        </is>
-      </c>
-      <c r="B269" s="3" t="inlineStr">
-        <is>
-          <t>Rovere</t>
-        </is>
-      </c>
+      <c r="A269" s="3" t="inlineStr"/>
+      <c r="B269" s="3" t="inlineStr"/>
       <c r="C269" s="3" t="inlineStr"/>
       <c r="D269" s="3" t="inlineStr"/>
-      <c r="E269" s="5" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/ana-rovere-7b4474111</t>
-        </is>
-      </c>
+      <c r="E269" s="3" t="inlineStr"/>
       <c r="F269" s="3" t="inlineStr">
         <is>
           <t>Costa Crociere IT</t>
         </is>
       </c>
-      <c r="G269" s="3" t="inlineStr">
-        <is>
-          <t>Digital Marketing Specialist South America</t>
-        </is>
-      </c>
+      <c r="G269" s="3" t="inlineStr"/>
       <c r="H269" s="3" t="inlineStr">
         <is>
           <t>costacrociere.it</t>
         </is>
       </c>
-      <c r="I269" s="3" t="inlineStr">
-        <is>
-          <t>br</t>
-        </is>
-      </c>
+      <c r="I269" s="3" t="inlineStr"/>
       <c r="J269" s="3" t="inlineStr"/>
       <c r="K269" s="3" t="inlineStr"/>
       <c r="L269" s="3" t="inlineStr"/>
@@ -13043,43 +12063,23 @@
       <c r="R277" s="3" t="inlineStr"/>
     </row>
     <row r="278">
-      <c r="A278" s="2" t="inlineStr">
-        <is>
-          <t>Claudio</t>
-        </is>
-      </c>
-      <c r="B278" s="2" t="inlineStr">
-        <is>
-          <t>Vitale</t>
-        </is>
-      </c>
+      <c r="A278" s="2" t="inlineStr"/>
+      <c r="B278" s="2" t="inlineStr"/>
       <c r="C278" s="2" t="inlineStr"/>
       <c r="D278" s="2" t="inlineStr"/>
-      <c r="E278" s="4" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/vitaleclaudio</t>
-        </is>
-      </c>
+      <c r="E278" s="2" t="inlineStr"/>
       <c r="F278" s="2" t="inlineStr">
         <is>
           <t>CRLab IT</t>
         </is>
       </c>
-      <c r="G278" s="2" t="inlineStr">
-        <is>
-          <t>Digital Marketing Manager</t>
-        </is>
-      </c>
+      <c r="G278" s="2" t="inlineStr"/>
       <c r="H278" s="2" t="inlineStr">
         <is>
           <t>crlab.com</t>
         </is>
       </c>
-      <c r="I278" s="2" t="inlineStr">
-        <is>
-          <t>it</t>
-        </is>
-      </c>
+      <c r="I278" s="2" t="inlineStr"/>
       <c r="J278" s="2" t="inlineStr">
         <is>
           <t>30 Giorni</t>
@@ -13299,43 +12299,23 @@
       <c r="R283" s="2" t="inlineStr"/>
     </row>
     <row r="284">
-      <c r="A284" s="3" t="inlineStr">
-        <is>
-          <t>Matteo</t>
-        </is>
-      </c>
-      <c r="B284" s="3" t="inlineStr">
-        <is>
-          <t>Meago</t>
-        </is>
-      </c>
+      <c r="A284" s="3" t="inlineStr"/>
+      <c r="B284" s="3" t="inlineStr"/>
       <c r="C284" s="3" t="inlineStr"/>
       <c r="D284" s="3" t="inlineStr"/>
-      <c r="E284" s="5" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/matteo-meago</t>
-        </is>
-      </c>
+      <c r="E284" s="3" t="inlineStr"/>
       <c r="F284" s="3" t="inlineStr">
         <is>
           <t>Crédit Agricole IT</t>
         </is>
       </c>
-      <c r="G284" s="3" t="inlineStr">
-        <is>
-          <t>Senior Digital Marketing Manager</t>
-        </is>
-      </c>
+      <c r="G284" s="3" t="inlineStr"/>
       <c r="H284" s="3" t="inlineStr">
         <is>
-          <t>credit-agricole.it</t>
-        </is>
-      </c>
-      <c r="I284" s="3" t="inlineStr">
-        <is>
-          <t>it</t>
-        </is>
-      </c>
+          <t>conti.credit-agricole.it</t>
+        </is>
+      </c>
+      <c r="I284" s="3" t="inlineStr"/>
       <c r="J284" s="3" t="inlineStr">
         <is>
           <t>30 Giorni</t>
@@ -13367,43 +12347,23 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="3" t="inlineStr">
-        <is>
-          <t>Francesca</t>
-        </is>
-      </c>
-      <c r="B285" s="3" t="inlineStr">
-        <is>
-          <t>Migli</t>
-        </is>
-      </c>
+      <c r="A285" s="3" t="inlineStr"/>
+      <c r="B285" s="3" t="inlineStr"/>
       <c r="C285" s="3" t="inlineStr"/>
       <c r="D285" s="3" t="inlineStr"/>
-      <c r="E285" s="5" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/francesca-migli-3a955b6</t>
-        </is>
-      </c>
+      <c r="E285" s="3" t="inlineStr"/>
       <c r="F285" s="3" t="inlineStr">
         <is>
           <t>Crédit Agricole IT</t>
         </is>
       </c>
-      <c r="G285" s="3" t="inlineStr">
-        <is>
-          <t>Responsabile Digital Marketing e Acquisition</t>
-        </is>
-      </c>
+      <c r="G285" s="3" t="inlineStr"/>
       <c r="H285" s="3" t="inlineStr">
         <is>
-          <t>credit-agricole.it</t>
-        </is>
-      </c>
-      <c r="I285" s="3" t="inlineStr">
-        <is>
-          <t>it</t>
-        </is>
-      </c>
+          <t>conti.credit-agricole.it</t>
+        </is>
+      </c>
+      <c r="I285" s="3" t="inlineStr"/>
       <c r="J285" s="3" t="inlineStr"/>
       <c r="K285" s="3" t="inlineStr"/>
       <c r="L285" s="3" t="inlineStr"/>
@@ -13731,43 +12691,23 @@
       <c r="R293" s="3" t="inlineStr"/>
     </row>
     <row r="294">
-      <c r="A294" s="2" t="inlineStr">
-        <is>
-          <t>Heloísa</t>
-        </is>
-      </c>
-      <c r="B294" s="2" t="inlineStr">
-        <is>
-          <t>Freygang</t>
-        </is>
-      </c>
+      <c r="A294" s="2" t="inlineStr"/>
+      <c r="B294" s="2" t="inlineStr"/>
       <c r="C294" s="2" t="inlineStr"/>
       <c r="D294" s="2" t="inlineStr"/>
-      <c r="E294" s="4" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/heloisafreygang</t>
-        </is>
-      </c>
+      <c r="E294" s="2" t="inlineStr"/>
       <c r="F294" s="2" t="inlineStr">
         <is>
           <t>Daniel Wellington IT</t>
         </is>
       </c>
-      <c r="G294" s="2" t="inlineStr">
-        <is>
-          <t>Influencer &amp; Digital Marketing Specialist</t>
-        </is>
-      </c>
+      <c r="G294" s="2" t="inlineStr"/>
       <c r="H294" s="2" t="inlineStr">
         <is>
           <t>danielwellington.com</t>
         </is>
       </c>
-      <c r="I294" s="2" t="inlineStr">
-        <is>
-          <t>se</t>
-        </is>
-      </c>
+      <c r="I294" s="2" t="inlineStr"/>
       <c r="J294" s="2" t="inlineStr">
         <is>
           <t>30 Giorni</t>
@@ -13991,43 +12931,23 @@
       <c r="R299" s="2" t="inlineStr"/>
     </row>
     <row r="300">
-      <c r="A300" s="3" t="inlineStr">
-        <is>
-          <t>Albert</t>
-        </is>
-      </c>
-      <c r="B300" s="3" t="inlineStr">
-        <is>
-          <t>Granados</t>
-        </is>
-      </c>
+      <c r="A300" s="3" t="inlineStr"/>
+      <c r="B300" s="3" t="inlineStr"/>
       <c r="C300" s="3" t="inlineStr"/>
       <c r="D300" s="3" t="inlineStr"/>
-      <c r="E300" s="5" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/albert-granados-ab130b33</t>
-        </is>
-      </c>
+      <c r="E300" s="3" t="inlineStr"/>
       <c r="F300" s="3" t="inlineStr">
         <is>
           <t>Decathlon IT</t>
         </is>
       </c>
-      <c r="G300" s="3" t="inlineStr">
-        <is>
-          <t>Head Of Digital Marketing</t>
-        </is>
-      </c>
+      <c r="G300" s="3" t="inlineStr"/>
       <c r="H300" s="3" t="inlineStr">
         <is>
-          <t>decathlon.com</t>
-        </is>
-      </c>
-      <c r="I300" s="3" t="inlineStr">
-        <is>
-          <t>us</t>
-        </is>
-      </c>
+          <t>decathlon.it</t>
+        </is>
+      </c>
+      <c r="I300" s="3" t="inlineStr"/>
       <c r="J300" s="3" t="inlineStr">
         <is>
           <t>30 Giorni</t>
@@ -14063,43 +12983,23 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="3" t="inlineStr">
-        <is>
-          <t>Nicolás</t>
-        </is>
-      </c>
-      <c r="B301" s="3" t="inlineStr">
-        <is>
-          <t>Fernández Casillas</t>
-        </is>
-      </c>
+      <c r="A301" s="3" t="inlineStr"/>
+      <c r="B301" s="3" t="inlineStr"/>
       <c r="C301" s="3" t="inlineStr"/>
       <c r="D301" s="3" t="inlineStr"/>
-      <c r="E301" s="5" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/nicolasfdez</t>
-        </is>
-      </c>
+      <c r="E301" s="3" t="inlineStr"/>
       <c r="F301" s="3" t="inlineStr">
         <is>
           <t>Decathlon IT</t>
         </is>
       </c>
-      <c r="G301" s="3" t="inlineStr">
-        <is>
-          <t>Senior Digital Product Marketing Manager</t>
-        </is>
-      </c>
+      <c r="G301" s="3" t="inlineStr"/>
       <c r="H301" s="3" t="inlineStr">
         <is>
-          <t>decathlon.com</t>
-        </is>
-      </c>
-      <c r="I301" s="3" t="inlineStr">
-        <is>
-          <t>nl</t>
-        </is>
-      </c>
+          <t>decathlon.it</t>
+        </is>
+      </c>
+      <c r="I301" s="3" t="inlineStr"/>
       <c r="J301" s="3" t="inlineStr"/>
       <c r="K301" s="3" t="inlineStr"/>
       <c r="L301" s="3" t="inlineStr"/>
@@ -14111,43 +13011,23 @@
       <c r="R301" s="3" t="inlineStr"/>
     </row>
     <row r="302">
-      <c r="A302" s="2" t="inlineStr">
-        <is>
-          <t>Albert</t>
-        </is>
-      </c>
-      <c r="B302" s="2" t="inlineStr">
-        <is>
-          <t>Granados</t>
-        </is>
-      </c>
+      <c r="A302" s="2" t="inlineStr"/>
+      <c r="B302" s="2" t="inlineStr"/>
       <c r="C302" s="2" t="inlineStr"/>
       <c r="D302" s="2" t="inlineStr"/>
-      <c r="E302" s="4" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/albert-granados-ab130b33</t>
-        </is>
-      </c>
+      <c r="E302" s="2" t="inlineStr"/>
       <c r="F302" s="2" t="inlineStr">
         <is>
           <t>Decathlon Rent IT</t>
         </is>
       </c>
-      <c r="G302" s="2" t="inlineStr">
-        <is>
-          <t>Head Of Digital Marketing</t>
-        </is>
-      </c>
+      <c r="G302" s="2" t="inlineStr"/>
       <c r="H302" s="2" t="inlineStr">
         <is>
-          <t>decathlon.com</t>
-        </is>
-      </c>
-      <c r="I302" s="2" t="inlineStr">
-        <is>
-          <t>us</t>
-        </is>
-      </c>
+          <t>rent.decathlon.it</t>
+        </is>
+      </c>
+      <c r="I302" s="2" t="inlineStr"/>
       <c r="J302" s="2" t="inlineStr">
         <is>
           <t>30 Giorni</t>
@@ -14183,43 +13063,23 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="2" t="inlineStr">
-        <is>
-          <t>Nicolás</t>
-        </is>
-      </c>
-      <c r="B303" s="2" t="inlineStr">
-        <is>
-          <t>Fernández Casillas</t>
-        </is>
-      </c>
+      <c r="A303" s="2" t="inlineStr"/>
+      <c r="B303" s="2" t="inlineStr"/>
       <c r="C303" s="2" t="inlineStr"/>
       <c r="D303" s="2" t="inlineStr"/>
-      <c r="E303" s="4" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/nicolasfdez</t>
-        </is>
-      </c>
+      <c r="E303" s="2" t="inlineStr"/>
       <c r="F303" s="2" t="inlineStr">
         <is>
           <t>Decathlon Rent IT</t>
         </is>
       </c>
-      <c r="G303" s="2" t="inlineStr">
-        <is>
-          <t>Senior Digital Product Marketing Manager</t>
-        </is>
-      </c>
+      <c r="G303" s="2" t="inlineStr"/>
       <c r="H303" s="2" t="inlineStr">
         <is>
-          <t>decathlon.com</t>
-        </is>
-      </c>
-      <c r="I303" s="2" t="inlineStr">
-        <is>
-          <t>nl</t>
-        </is>
-      </c>
+          <t>rent.decathlon.it</t>
+        </is>
+      </c>
+      <c r="I303" s="2" t="inlineStr"/>
       <c r="J303" s="2" t="inlineStr"/>
       <c r="K303" s="2" t="inlineStr"/>
       <c r="L303" s="2" t="inlineStr"/>
@@ -14475,43 +13335,23 @@
       <c r="R309" s="3" t="inlineStr"/>
     </row>
     <row r="310">
-      <c r="A310" s="2" t="inlineStr">
-        <is>
-          <t>Sosuke</t>
-        </is>
-      </c>
-      <c r="B310" s="2" t="inlineStr">
-        <is>
-          <t>I.</t>
-        </is>
-      </c>
+      <c r="A310" s="2" t="inlineStr"/>
+      <c r="B310" s="2" t="inlineStr"/>
       <c r="C310" s="2" t="inlineStr"/>
       <c r="D310" s="2" t="inlineStr"/>
-      <c r="E310" s="4" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/sosukeinoue</t>
-        </is>
-      </c>
+      <c r="E310" s="2" t="inlineStr"/>
       <c r="F310" s="2" t="inlineStr">
         <is>
           <t>Delonghi IT</t>
         </is>
       </c>
-      <c r="G310" s="2" t="inlineStr">
-        <is>
-          <t>Senior Manager, Digital Marketing &amp; IT</t>
-        </is>
-      </c>
+      <c r="G310" s="2" t="inlineStr"/>
       <c r="H310" s="2" t="inlineStr">
         <is>
           <t>delonghi.com</t>
         </is>
       </c>
-      <c r="I310" s="2" t="inlineStr">
-        <is>
-          <t>jp</t>
-        </is>
-      </c>
+      <c r="I310" s="2" t="inlineStr"/>
       <c r="J310" s="2" t="inlineStr">
         <is>
           <t>15 Giorni</t>
@@ -14547,43 +13387,23 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="2" t="inlineStr">
-        <is>
-          <t>Melissa</t>
-        </is>
-      </c>
-      <c r="B311" s="2" t="inlineStr">
-        <is>
-          <t>Lubert</t>
-        </is>
-      </c>
+      <c r="A311" s="2" t="inlineStr"/>
+      <c r="B311" s="2" t="inlineStr"/>
       <c r="C311" s="2" t="inlineStr"/>
       <c r="D311" s="2" t="inlineStr"/>
-      <c r="E311" s="4" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/melissa-lubert-561b0318</t>
-        </is>
-      </c>
+      <c r="E311" s="2" t="inlineStr"/>
       <c r="F311" s="2" t="inlineStr">
         <is>
           <t>Delonghi IT</t>
         </is>
       </c>
-      <c r="G311" s="2" t="inlineStr">
-        <is>
-          <t>Digital Retail Marketing Manager</t>
-        </is>
-      </c>
+      <c r="G311" s="2" t="inlineStr"/>
       <c r="H311" s="2" t="inlineStr">
         <is>
           <t>delonghi.com</t>
         </is>
       </c>
-      <c r="I311" s="2" t="inlineStr">
-        <is>
-          <t>us</t>
-        </is>
-      </c>
+      <c r="I311" s="2" t="inlineStr"/>
       <c r="J311" s="2" t="inlineStr"/>
       <c r="K311" s="2" t="inlineStr"/>
       <c r="L311" s="2" t="inlineStr"/>
@@ -14747,43 +13567,23 @@
       <c r="R315" s="2" t="inlineStr"/>
     </row>
     <row r="316">
-      <c r="A316" s="3" t="inlineStr">
-        <is>
-          <t>Sonia</t>
-        </is>
-      </c>
-      <c r="B316" s="3" t="inlineStr">
-        <is>
-          <t>G.</t>
-        </is>
-      </c>
+      <c r="A316" s="3" t="inlineStr"/>
+      <c r="B316" s="3" t="inlineStr"/>
       <c r="C316" s="3" t="inlineStr"/>
       <c r="D316" s="3" t="inlineStr"/>
-      <c r="E316" s="5" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/sgomez12</t>
-        </is>
-      </c>
+      <c r="E316" s="3" t="inlineStr"/>
       <c r="F316" s="3" t="inlineStr">
         <is>
           <t>Deporvillage IT</t>
         </is>
       </c>
-      <c r="G316" s="3" t="inlineStr">
-        <is>
-          <t>Performance Digital Marketing</t>
-        </is>
-      </c>
+      <c r="G316" s="3" t="inlineStr"/>
       <c r="H316" s="3" t="inlineStr">
         <is>
-          <t>deporvillage.com</t>
-        </is>
-      </c>
-      <c r="I316" s="3" t="inlineStr">
-        <is>
-          <t>es</t>
-        </is>
-      </c>
+          <t>deporvillage.it</t>
+        </is>
+      </c>
+      <c r="I316" s="3" t="inlineStr"/>
       <c r="J316" s="3" t="inlineStr">
         <is>
           <t>30 Giorni</t>
@@ -14819,43 +13619,23 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="3" t="inlineStr">
-        <is>
-          <t>Helena</t>
-        </is>
-      </c>
-      <c r="B317" s="3" t="inlineStr">
-        <is>
-          <t>Mariño Jiménez</t>
-        </is>
-      </c>
+      <c r="A317" s="3" t="inlineStr"/>
+      <c r="B317" s="3" t="inlineStr"/>
       <c r="C317" s="3" t="inlineStr"/>
       <c r="D317" s="3" t="inlineStr"/>
-      <c r="E317" s="5" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/helena-mariño-jiménez-a65077a1</t>
-        </is>
-      </c>
+      <c r="E317" s="3" t="inlineStr"/>
       <c r="F317" s="3" t="inlineStr">
         <is>
           <t>Deporvillage IT</t>
         </is>
       </c>
-      <c r="G317" s="3" t="inlineStr">
-        <is>
-          <t>Performance Marketing Manager</t>
-        </is>
-      </c>
+      <c r="G317" s="3" t="inlineStr"/>
       <c r="H317" s="3" t="inlineStr">
         <is>
-          <t>deporvillage.com</t>
-        </is>
-      </c>
-      <c r="I317" s="3" t="inlineStr">
-        <is>
-          <t>es</t>
-        </is>
-      </c>
+          <t>deporvillage.it</t>
+        </is>
+      </c>
+      <c r="I317" s="3" t="inlineStr"/>
       <c r="J317" s="3" t="inlineStr"/>
       <c r="K317" s="3" t="inlineStr"/>
       <c r="L317" s="3" t="inlineStr"/>
@@ -15667,43 +14447,23 @@
       <c r="R337" s="3" t="inlineStr"/>
     </row>
     <row r="338">
-      <c r="A338" s="2" t="inlineStr">
-        <is>
-          <t>Mariona</t>
-        </is>
-      </c>
-      <c r="B338" s="2" t="inlineStr">
-        <is>
-          <t>Quirante Saderra</t>
-        </is>
-      </c>
+      <c r="A338" s="2" t="inlineStr"/>
+      <c r="B338" s="2" t="inlineStr"/>
       <c r="C338" s="2" t="inlineStr"/>
       <c r="D338" s="2" t="inlineStr"/>
-      <c r="E338" s="4" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/marionaquirantesaderra</t>
-        </is>
-      </c>
+      <c r="E338" s="2" t="inlineStr"/>
       <c r="F338" s="2" t="inlineStr">
         <is>
           <t>Dogfy Diet Italia</t>
         </is>
       </c>
-      <c r="G338" s="2" t="inlineStr">
-        <is>
-          <t>Digital Marketing &amp; Content ES</t>
-        </is>
-      </c>
+      <c r="G338" s="2" t="inlineStr"/>
       <c r="H338" s="2" t="inlineStr">
         <is>
           <t>dogfydiet.com</t>
         </is>
       </c>
-      <c r="I338" s="2" t="inlineStr">
-        <is>
-          <t>es</t>
-        </is>
-      </c>
+      <c r="I338" s="2" t="inlineStr"/>
       <c r="J338" s="2" t="inlineStr">
         <is>
           <t>30 Giorni</t>
@@ -16003,43 +14763,23 @@
       <c r="R345" s="3" t="inlineStr"/>
     </row>
     <row r="346">
-      <c r="A346" s="2" t="inlineStr">
-        <is>
-          <t>Andrea</t>
-        </is>
-      </c>
-      <c r="B346" s="2" t="inlineStr">
-        <is>
-          <t>Perugini</t>
-        </is>
-      </c>
+      <c r="A346" s="2" t="inlineStr"/>
+      <c r="B346" s="2" t="inlineStr"/>
       <c r="C346" s="2" t="inlineStr"/>
       <c r="D346" s="2" t="inlineStr"/>
-      <c r="E346" s="4" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/andrea-perugini-272a07211</t>
-        </is>
-      </c>
+      <c r="E346" s="2" t="inlineStr"/>
       <c r="F346" s="2" t="inlineStr">
         <is>
           <t>Dorelan IT</t>
         </is>
       </c>
-      <c r="G346" s="2" t="inlineStr">
-        <is>
-          <t>Digital marketing</t>
-        </is>
-      </c>
+      <c r="G346" s="2" t="inlineStr"/>
       <c r="H346" s="2" t="inlineStr">
         <is>
           <t>dorelan.com</t>
         </is>
       </c>
-      <c r="I346" s="2" t="inlineStr">
-        <is>
-          <t>it</t>
-        </is>
-      </c>
+      <c r="I346" s="2" t="inlineStr"/>
       <c r="J346" s="2" t="inlineStr">
         <is>
           <t>30 Giorni</t>
@@ -16103,43 +14843,23 @@
       <c r="R347" s="2" t="inlineStr"/>
     </row>
     <row r="348">
-      <c r="A348" s="3" t="inlineStr">
-        <is>
-          <t>Giada</t>
-        </is>
-      </c>
-      <c r="B348" s="3" t="inlineStr">
-        <is>
-          <t>Conti</t>
-        </is>
-      </c>
+      <c r="A348" s="3" t="inlineStr"/>
+      <c r="B348" s="3" t="inlineStr"/>
       <c r="C348" s="3" t="inlineStr"/>
       <c r="D348" s="3" t="inlineStr"/>
-      <c r="E348" s="5" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/giada-conti</t>
-        </is>
-      </c>
+      <c r="E348" s="3" t="inlineStr"/>
       <c r="F348" s="3" t="inlineStr">
         <is>
           <t>Douglas_IT</t>
         </is>
       </c>
-      <c r="G348" s="3" t="inlineStr">
-        <is>
-          <t>Online supplier campaign Specialist</t>
-        </is>
-      </c>
+      <c r="G348" s="3" t="inlineStr"/>
       <c r="H348" s="3" t="inlineStr">
         <is>
           <t>douglas.it</t>
         </is>
       </c>
-      <c r="I348" s="3" t="inlineStr">
-        <is>
-          <t>it</t>
-        </is>
-      </c>
+      <c r="I348" s="3" t="inlineStr"/>
       <c r="J348" s="3" t="inlineStr">
         <is>
           <t>30 Giorni</t>
@@ -16280,43 +15000,23 @@
       <c r="R351" s="2" t="inlineStr"/>
     </row>
     <row r="352">
-      <c r="A352" s="3" t="inlineStr">
-        <is>
-          <t>Francesca</t>
-        </is>
-      </c>
-      <c r="B352" s="3" t="inlineStr">
-        <is>
-          <t>Montanari</t>
-        </is>
-      </c>
+      <c r="A352" s="3" t="inlineStr"/>
+      <c r="B352" s="3" t="inlineStr"/>
       <c r="C352" s="3" t="inlineStr"/>
       <c r="D352" s="3" t="inlineStr"/>
-      <c r="E352" s="5" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/francymontanari</t>
-        </is>
-      </c>
+      <c r="E352" s="3" t="inlineStr"/>
       <c r="F352" s="3" t="inlineStr">
         <is>
           <t>Dr. Vranjes Firenze IT</t>
         </is>
       </c>
-      <c r="G352" s="3" t="inlineStr">
-        <is>
-          <t>CRM &amp; Digital Marketing Manager</t>
-        </is>
-      </c>
+      <c r="G352" s="3" t="inlineStr"/>
       <c r="H352" s="3" t="inlineStr">
         <is>
-          <t>drvranjes.com</t>
-        </is>
-      </c>
-      <c r="I352" s="3" t="inlineStr">
-        <is>
-          <t>it</t>
-        </is>
-      </c>
+          <t>drvranjes.it</t>
+        </is>
+      </c>
+      <c r="I352" s="3" t="inlineStr"/>
       <c r="J352" s="3" t="inlineStr">
         <is>
           <t>30 Giorni</t>
@@ -16352,43 +15052,23 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353" s="3" t="inlineStr">
-        <is>
-          <t>Elettra</t>
-        </is>
-      </c>
-      <c r="B353" s="3" t="inlineStr">
-        <is>
-          <t>Pini</t>
-        </is>
-      </c>
+      <c r="A353" s="3" t="inlineStr"/>
+      <c r="B353" s="3" t="inlineStr"/>
       <c r="C353" s="3" t="inlineStr"/>
       <c r="D353" s="3" t="inlineStr"/>
-      <c r="E353" s="5" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/elettra-pini-540a47283</t>
-        </is>
-      </c>
+      <c r="E353" s="3" t="inlineStr"/>
       <c r="F353" s="3" t="inlineStr">
         <is>
           <t>Dr. Vranjes Firenze IT</t>
         </is>
       </c>
-      <c r="G353" s="3" t="inlineStr">
-        <is>
-          <t>Digital Marketing specialist</t>
-        </is>
-      </c>
+      <c r="G353" s="3" t="inlineStr"/>
       <c r="H353" s="3" t="inlineStr">
         <is>
-          <t>drvranjes.com</t>
-        </is>
-      </c>
-      <c r="I353" s="3" t="inlineStr">
-        <is>
-          <t>it</t>
-        </is>
-      </c>
+          <t>drvranjes.it</t>
+        </is>
+      </c>
+      <c r="I353" s="3" t="inlineStr"/>
       <c r="J353" s="3" t="inlineStr"/>
       <c r="K353" s="3" t="inlineStr"/>
       <c r="L353" s="3" t="inlineStr"/>
@@ -16400,43 +15080,23 @@
       <c r="R353" s="3" t="inlineStr"/>
     </row>
     <row r="354">
-      <c r="A354" s="2" t="inlineStr">
-        <is>
-          <t>Saverio</t>
-        </is>
-      </c>
-      <c r="B354" s="2" t="inlineStr">
-        <is>
-          <t>Vacca</t>
-        </is>
-      </c>
+      <c r="A354" s="2" t="inlineStr"/>
+      <c r="B354" s="2" t="inlineStr"/>
       <c r="C354" s="2" t="inlineStr"/>
       <c r="D354" s="2" t="inlineStr"/>
-      <c r="E354" s="4" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/saverio-vacca-993a1630</t>
-        </is>
-      </c>
+      <c r="E354" s="2" t="inlineStr"/>
       <c r="F354" s="2" t="inlineStr">
         <is>
           <t>Drestige IT</t>
         </is>
       </c>
-      <c r="G354" s="2" t="inlineStr">
-        <is>
-          <t>Responsabile Digital Marketing e Performance</t>
-        </is>
-      </c>
+      <c r="G354" s="2" t="inlineStr"/>
       <c r="H354" s="2" t="inlineStr">
         <is>
           <t>drestige.com</t>
         </is>
       </c>
-      <c r="I354" s="2" t="inlineStr">
-        <is>
-          <t>it</t>
-        </is>
-      </c>
+      <c r="I354" s="2" t="inlineStr"/>
       <c r="J354" s="2" t="inlineStr">
         <is>
           <t>30 Giorni</t>
@@ -16500,43 +15160,23 @@
       <c r="R355" s="2" t="inlineStr"/>
     </row>
     <row r="356">
-      <c r="A356" s="3" t="inlineStr">
-        <is>
-          <t>Julian</t>
-        </is>
-      </c>
-      <c r="B356" s="3" t="inlineStr">
-        <is>
-          <t>Cöln</t>
-        </is>
-      </c>
+      <c r="A356" s="3" t="inlineStr"/>
+      <c r="B356" s="3" t="inlineStr"/>
       <c r="C356" s="3" t="inlineStr"/>
       <c r="D356" s="3" t="inlineStr"/>
-      <c r="E356" s="5" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/julian-cöln-0944ba2b6</t>
-        </is>
-      </c>
+      <c r="E356" s="3" t="inlineStr"/>
       <c r="F356" s="3" t="inlineStr">
         <is>
           <t>Dyson IT</t>
         </is>
       </c>
-      <c r="G356" s="3" t="inlineStr">
-        <is>
-          <t>Affiliate Manager</t>
-        </is>
-      </c>
+      <c r="G356" s="3" t="inlineStr"/>
       <c r="H356" s="3" t="inlineStr">
         <is>
-          <t>dyson.com</t>
-        </is>
-      </c>
-      <c r="I356" s="3" t="inlineStr">
-        <is>
-          <t>de</t>
-        </is>
-      </c>
+          <t>dyson.it</t>
+        </is>
+      </c>
+      <c r="I356" s="3" t="inlineStr"/>
       <c r="J356" s="3" t="inlineStr">
         <is>
           <t>30 Giorni</t>
@@ -16572,43 +15212,23 @@
       </c>
     </row>
     <row r="357">
-      <c r="A357" s="3" t="inlineStr">
-        <is>
-          <t>Paola</t>
-        </is>
-      </c>
-      <c r="B357" s="3" t="inlineStr">
-        <is>
-          <t>Panseri</t>
-        </is>
-      </c>
+      <c r="A357" s="3" t="inlineStr"/>
+      <c r="B357" s="3" t="inlineStr"/>
       <c r="C357" s="3" t="inlineStr"/>
       <c r="D357" s="3" t="inlineStr"/>
-      <c r="E357" s="5" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/paola-panseri-9ba28758</t>
-        </is>
-      </c>
+      <c r="E357" s="3" t="inlineStr"/>
       <c r="F357" s="3" t="inlineStr">
         <is>
           <t>Dyson IT</t>
         </is>
       </c>
-      <c r="G357" s="3" t="inlineStr">
-        <is>
-          <t>Senior Affiliate Manager for Southern Europe | FR | IT | ES | PT</t>
-        </is>
-      </c>
+      <c r="G357" s="3" t="inlineStr"/>
       <c r="H357" s="3" t="inlineStr">
         <is>
-          <t>dyson.com</t>
-        </is>
-      </c>
-      <c r="I357" s="3" t="inlineStr">
-        <is>
-          <t>it</t>
-        </is>
-      </c>
+          <t>dyson.it</t>
+        </is>
+      </c>
+      <c r="I357" s="3" t="inlineStr"/>
       <c r="J357" s="3" t="inlineStr"/>
       <c r="K357" s="3" t="inlineStr"/>
       <c r="L357" s="3" t="inlineStr"/>
@@ -17184,43 +15804,23 @@
       <c r="R371" s="2" t="inlineStr"/>
     </row>
     <row r="372">
-      <c r="A372" s="3" t="inlineStr">
-        <is>
-          <t>Ilaria</t>
-        </is>
-      </c>
-      <c r="B372" s="3" t="inlineStr">
-        <is>
-          <t>Incarnato</t>
-        </is>
-      </c>
+      <c r="A372" s="3" t="inlineStr"/>
+      <c r="B372" s="3" t="inlineStr"/>
       <c r="C372" s="3" t="inlineStr"/>
       <c r="D372" s="3" t="inlineStr"/>
-      <c r="E372" s="5" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/ilaria-incarnato-67b755209</t>
-        </is>
-      </c>
+      <c r="E372" s="3" t="inlineStr"/>
       <c r="F372" s="3" t="inlineStr">
         <is>
           <t>efarma IT</t>
         </is>
       </c>
-      <c r="G372" s="3" t="inlineStr">
-        <is>
-          <t>Digital Store Manager, Seo Copywriter &amp; Digital PR</t>
-        </is>
-      </c>
+      <c r="G372" s="3" t="inlineStr"/>
       <c r="H372" s="3" t="inlineStr">
         <is>
           <t>efarma.com</t>
         </is>
       </c>
-      <c r="I372" s="3" t="inlineStr">
-        <is>
-          <t>it</t>
-        </is>
-      </c>
+      <c r="I372" s="3" t="inlineStr"/>
       <c r="J372" s="3" t="inlineStr">
         <is>
           <t>30 Giorni</t>
@@ -17524,43 +16124,23 @@
       <c r="R379" s="2" t="inlineStr"/>
     </row>
     <row r="380">
-      <c r="A380" s="3" t="inlineStr">
-        <is>
-          <t>Daniela</t>
-        </is>
-      </c>
-      <c r="B380" s="3" t="inlineStr">
-        <is>
-          <t>Miccoli</t>
-        </is>
-      </c>
+      <c r="A380" s="3" t="inlineStr"/>
+      <c r="B380" s="3" t="inlineStr"/>
       <c r="C380" s="3" t="inlineStr"/>
       <c r="D380" s="3" t="inlineStr"/>
-      <c r="E380" s="5" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/danielamiccoli</t>
-        </is>
-      </c>
+      <c r="E380" s="3" t="inlineStr"/>
       <c r="F380" s="3" t="inlineStr">
         <is>
           <t>Elisabetta Franchi IT</t>
         </is>
       </c>
-      <c r="G380" s="3" t="inlineStr">
-        <is>
-          <t>Digital Marketing Manager</t>
-        </is>
-      </c>
+      <c r="G380" s="3" t="inlineStr"/>
       <c r="H380" s="3" t="inlineStr">
         <is>
           <t>elisabettafranchi.com</t>
         </is>
       </c>
-      <c r="I380" s="3" t="inlineStr">
-        <is>
-          <t>it</t>
-        </is>
-      </c>
+      <c r="I380" s="3" t="inlineStr"/>
       <c r="J380" s="3" t="inlineStr">
         <is>
           <t>20 Giorni</t>
@@ -17596,43 +16176,23 @@
       </c>
     </row>
     <row r="381">
-      <c r="A381" s="3" t="inlineStr">
-        <is>
-          <t>Isabella</t>
-        </is>
-      </c>
-      <c r="B381" s="3" t="inlineStr">
-        <is>
-          <t>Leo</t>
-        </is>
-      </c>
+      <c r="A381" s="3" t="inlineStr"/>
+      <c r="B381" s="3" t="inlineStr"/>
       <c r="C381" s="3" t="inlineStr"/>
       <c r="D381" s="3" t="inlineStr"/>
-      <c r="E381" s="5" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/isabella-leo-00b74a152</t>
-        </is>
-      </c>
+      <c r="E381" s="3" t="inlineStr"/>
       <c r="F381" s="3" t="inlineStr">
         <is>
           <t>Elisabetta Franchi IT</t>
         </is>
       </c>
-      <c r="G381" s="3" t="inlineStr">
-        <is>
-          <t>E-Commerce Digital Content</t>
-        </is>
-      </c>
+      <c r="G381" s="3" t="inlineStr"/>
       <c r="H381" s="3" t="inlineStr">
         <is>
           <t>elisabettafranchi.com</t>
         </is>
       </c>
-      <c r="I381" s="3" t="inlineStr">
-        <is>
-          <t>it</t>
-        </is>
-      </c>
+      <c r="I381" s="3" t="inlineStr"/>
       <c r="J381" s="3" t="inlineStr"/>
       <c r="K381" s="3" t="inlineStr"/>
       <c r="L381" s="3" t="inlineStr"/>
@@ -17884,43 +16444,23 @@
       <c r="R387" s="2" t="inlineStr"/>
     </row>
     <row r="388">
-      <c r="A388" s="3" t="inlineStr">
-        <is>
-          <t>Aleks</t>
-        </is>
-      </c>
-      <c r="B388" s="3" t="inlineStr">
-        <is>
-          <t>Vasilev</t>
-        </is>
-      </c>
+      <c r="A388" s="3" t="inlineStr"/>
+      <c r="B388" s="3" t="inlineStr"/>
       <c r="C388" s="3" t="inlineStr"/>
       <c r="D388" s="3" t="inlineStr"/>
-      <c r="E388" s="5" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/aleks02</t>
-        </is>
-      </c>
+      <c r="E388" s="3" t="inlineStr"/>
       <c r="F388" s="3" t="inlineStr">
         <is>
           <t>Eneba IT</t>
         </is>
       </c>
-      <c r="G388" s="3" t="inlineStr">
-        <is>
-          <t>Affiliate Marketing Manager</t>
-        </is>
-      </c>
+      <c r="G388" s="3" t="inlineStr"/>
       <c r="H388" s="3" t="inlineStr">
         <is>
           <t>eneba.com</t>
         </is>
       </c>
-      <c r="I388" s="3" t="inlineStr">
-        <is>
-          <t>bg</t>
-        </is>
-      </c>
+      <c r="I388" s="3" t="inlineStr"/>
       <c r="J388" s="3" t="inlineStr">
         <is>
           <t>30 Giorni</t>
@@ -17964,43 +16504,23 @@
       </c>
     </row>
     <row r="389">
-      <c r="A389" s="3" t="inlineStr">
-        <is>
-          <t>Justina</t>
-        </is>
-      </c>
-      <c r="B389" s="3" t="inlineStr">
-        <is>
-          <t>Pranciulė</t>
-        </is>
-      </c>
+      <c r="A389" s="3" t="inlineStr"/>
+      <c r="B389" s="3" t="inlineStr"/>
       <c r="C389" s="3" t="inlineStr"/>
       <c r="D389" s="3" t="inlineStr"/>
-      <c r="E389" s="5" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/justina-pranciulė</t>
-        </is>
-      </c>
+      <c r="E389" s="3" t="inlineStr"/>
       <c r="F389" s="3" t="inlineStr">
         <is>
           <t>Eneba IT</t>
         </is>
       </c>
-      <c r="G389" s="3" t="inlineStr">
-        <is>
-          <t>Affiliate Manager</t>
-        </is>
-      </c>
+      <c r="G389" s="3" t="inlineStr"/>
       <c r="H389" s="3" t="inlineStr">
         <is>
           <t>eneba.com</t>
         </is>
       </c>
-      <c r="I389" s="3" t="inlineStr">
-        <is>
-          <t>lt</t>
-        </is>
-      </c>
+      <c r="I389" s="3" t="inlineStr"/>
       <c r="J389" s="3" t="inlineStr"/>
       <c r="K389" s="3" t="inlineStr"/>
       <c r="L389" s="3" t="inlineStr"/>
@@ -18012,43 +16532,23 @@
       <c r="R389" s="3" t="inlineStr"/>
     </row>
     <row r="390">
-      <c r="A390" s="2" t="inlineStr">
-        <is>
-          <t>giulio</t>
-        </is>
-      </c>
-      <c r="B390" s="2" t="inlineStr">
-        <is>
-          <t>giusti</t>
-        </is>
-      </c>
+      <c r="A390" s="2" t="inlineStr"/>
+      <c r="B390" s="2" t="inlineStr"/>
       <c r="C390" s="2" t="inlineStr"/>
       <c r="D390" s="2" t="inlineStr"/>
-      <c r="E390" s="4" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/giulio-giusti-075910204</t>
-        </is>
-      </c>
+      <c r="E390" s="2" t="inlineStr"/>
       <c r="F390" s="2" t="inlineStr">
         <is>
           <t>Enervit IT</t>
         </is>
       </c>
-      <c r="G390" s="2" t="inlineStr">
-        <is>
-          <t>Digital marketing &amp; e-commerce director</t>
-        </is>
-      </c>
+      <c r="G390" s="2" t="inlineStr"/>
       <c r="H390" s="2" t="inlineStr">
         <is>
           <t>enervit.com</t>
         </is>
       </c>
-      <c r="I390" s="2" t="inlineStr">
-        <is>
-          <t>it</t>
-        </is>
-      </c>
+      <c r="I390" s="2" t="inlineStr"/>
       <c r="J390" s="2" t="inlineStr">
         <is>
           <t>30 Giorni</t>
@@ -18084,43 +16584,23 @@
       </c>
     </row>
     <row r="391">
-      <c r="A391" s="2" t="inlineStr">
-        <is>
-          <t>Alessandro</t>
-        </is>
-      </c>
-      <c r="B391" s="2" t="inlineStr">
-        <is>
-          <t>Confalonieri</t>
-        </is>
-      </c>
+      <c r="A391" s="2" t="inlineStr"/>
+      <c r="B391" s="2" t="inlineStr"/>
       <c r="C391" s="2" t="inlineStr"/>
       <c r="D391" s="2" t="inlineStr"/>
-      <c r="E391" s="4" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/alessandro-confalonieri-a60a29140</t>
-        </is>
-      </c>
+      <c r="E391" s="2" t="inlineStr"/>
       <c r="F391" s="2" t="inlineStr">
         <is>
           <t>Enervit IT</t>
         </is>
       </c>
-      <c r="G391" s="2" t="inlineStr">
-        <is>
-          <t>Digital Marketing Manager</t>
-        </is>
-      </c>
+      <c r="G391" s="2" t="inlineStr"/>
       <c r="H391" s="2" t="inlineStr">
         <is>
           <t>enervit.com</t>
         </is>
       </c>
-      <c r="I391" s="2" t="inlineStr">
-        <is>
-          <t>it</t>
-        </is>
-      </c>
+      <c r="I391" s="2" t="inlineStr"/>
       <c r="J391" s="2" t="inlineStr"/>
       <c r="K391" s="2" t="inlineStr"/>
       <c r="L391" s="2" t="inlineStr"/>
@@ -18212,43 +16692,23 @@
       <c r="R393" s="3" t="inlineStr"/>
     </row>
     <row r="394">
-      <c r="A394" s="2" t="inlineStr">
-        <is>
-          <t>Kristian</t>
-        </is>
-      </c>
-      <c r="B394" s="2" t="inlineStr">
-        <is>
-          <t>Tovt</t>
-        </is>
-      </c>
+      <c r="A394" s="2" t="inlineStr"/>
+      <c r="B394" s="2" t="inlineStr"/>
       <c r="C394" s="2" t="inlineStr"/>
       <c r="D394" s="2" t="inlineStr"/>
-      <c r="E394" s="4" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/kristian-tovt-888683284</t>
-        </is>
-      </c>
+      <c r="E394" s="2" t="inlineStr"/>
       <c r="F394" s="2" t="inlineStr">
         <is>
           <t>Enjoy the Wood</t>
         </is>
       </c>
-      <c r="G394" s="2" t="inlineStr">
-        <is>
-          <t>Affiliate Marketing Manager</t>
-        </is>
-      </c>
+      <c r="G394" s="2" t="inlineStr"/>
       <c r="H394" s="2" t="inlineStr">
         <is>
           <t>enjoythewood.com</t>
         </is>
       </c>
-      <c r="I394" s="2" t="inlineStr">
-        <is>
-          <t>ua</t>
-        </is>
-      </c>
+      <c r="I394" s="2" t="inlineStr"/>
       <c r="J394" s="2" t="inlineStr"/>
       <c r="K394" s="2" t="inlineStr">
         <is>
@@ -18288,43 +16748,23 @@
       </c>
     </row>
     <row r="395">
-      <c r="A395" s="2" t="inlineStr">
-        <is>
-          <t>Ilya</t>
-        </is>
-      </c>
-      <c r="B395" s="2" t="inlineStr">
-        <is>
-          <t>Savitsky</t>
-        </is>
-      </c>
+      <c r="A395" s="2" t="inlineStr"/>
+      <c r="B395" s="2" t="inlineStr"/>
       <c r="C395" s="2" t="inlineStr"/>
       <c r="D395" s="2" t="inlineStr"/>
-      <c r="E395" s="4" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/ilya-savitsky-5653761a8</t>
-        </is>
-      </c>
+      <c r="E395" s="2" t="inlineStr"/>
       <c r="F395" s="2" t="inlineStr">
         <is>
           <t>Enjoy the Wood</t>
         </is>
       </c>
-      <c r="G395" s="2" t="inlineStr">
-        <is>
-          <t>Affiliate Manager</t>
-        </is>
-      </c>
+      <c r="G395" s="2" t="inlineStr"/>
       <c r="H395" s="2" t="inlineStr">
         <is>
           <t>enjoythewood.com</t>
         </is>
       </c>
-      <c r="I395" s="2" t="inlineStr">
-        <is>
-          <t>ua</t>
-        </is>
-      </c>
+      <c r="I395" s="2" t="inlineStr"/>
       <c r="J395" s="2" t="inlineStr"/>
       <c r="K395" s="2" t="inlineStr"/>
       <c r="L395" s="2" t="inlineStr"/>
@@ -18416,43 +16856,23 @@
       <c r="R397" s="3" t="inlineStr"/>
     </row>
     <row r="398">
-      <c r="A398" s="2" t="inlineStr">
-        <is>
-          <t>Jimena</t>
-        </is>
-      </c>
-      <c r="B398" s="2" t="inlineStr">
-        <is>
-          <t>A. García Sotes</t>
-        </is>
-      </c>
+      <c r="A398" s="2" t="inlineStr"/>
+      <c r="B398" s="2" t="inlineStr"/>
       <c r="C398" s="2" t="inlineStr"/>
       <c r="D398" s="2" t="inlineStr"/>
-      <c r="E398" s="4" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/jimena-garcia-sotes</t>
-        </is>
-      </c>
+      <c r="E398" s="2" t="inlineStr"/>
       <c r="F398" s="2" t="inlineStr">
         <is>
           <t>Esdemarca IT</t>
         </is>
       </c>
-      <c r="G398" s="2" t="inlineStr">
-        <is>
-          <t>Especilaista en Marketing Digital</t>
-        </is>
-      </c>
+      <c r="G398" s="2" t="inlineStr"/>
       <c r="H398" s="2" t="inlineStr">
         <is>
           <t>esdemarca.com</t>
         </is>
       </c>
-      <c r="I398" s="2" t="inlineStr">
-        <is>
-          <t>es</t>
-        </is>
-      </c>
+      <c r="I398" s="2" t="inlineStr"/>
       <c r="J398" s="2" t="inlineStr">
         <is>
           <t>30 Giorni</t>
@@ -18844,43 +17264,23 @@
       <c r="R407" s="2" t="inlineStr"/>
     </row>
     <row r="408">
-      <c r="A408" s="3" t="inlineStr">
-        <is>
-          <t>Elisa</t>
-        </is>
-      </c>
-      <c r="B408" s="3" t="inlineStr">
-        <is>
-          <t>Baitella</t>
-        </is>
-      </c>
+      <c r="A408" s="3" t="inlineStr"/>
+      <c r="B408" s="3" t="inlineStr"/>
       <c r="C408" s="3" t="inlineStr"/>
       <c r="D408" s="3" t="inlineStr"/>
-      <c r="E408" s="5" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/elisa-baitella-251100101</t>
-        </is>
-      </c>
+      <c r="E408" s="3" t="inlineStr"/>
       <c r="F408" s="3" t="inlineStr">
         <is>
           <t>Eurobrico IT</t>
         </is>
       </c>
-      <c r="G408" s="3" t="inlineStr">
-        <is>
-          <t>Referente Digital Marketing</t>
-        </is>
-      </c>
+      <c r="G408" s="3" t="inlineStr"/>
       <c r="H408" s="3" t="inlineStr">
         <is>
           <t>eurobrico.com</t>
         </is>
       </c>
-      <c r="I408" s="3" t="inlineStr">
-        <is>
-          <t>it</t>
-        </is>
-      </c>
+      <c r="I408" s="3" t="inlineStr"/>
       <c r="J408" s="3" t="inlineStr">
         <is>
           <t>30 Giorni</t>
@@ -19104,43 +17504,23 @@
       <c r="R413" s="3" t="inlineStr"/>
     </row>
     <row r="414">
-      <c r="A414" s="2" t="inlineStr">
-        <is>
-          <t>Silvia</t>
-        </is>
-      </c>
-      <c r="B414" s="2" t="inlineStr">
-        <is>
-          <t>Alonso</t>
-        </is>
-      </c>
+      <c r="A414" s="2" t="inlineStr"/>
+      <c r="B414" s="2" t="inlineStr"/>
       <c r="C414" s="2" t="inlineStr"/>
       <c r="D414" s="2" t="inlineStr"/>
-      <c r="E414" s="4" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/silvia-alonso-mancera</t>
-        </is>
-      </c>
+      <c r="E414" s="2" t="inlineStr"/>
       <c r="F414" s="2" t="inlineStr">
         <is>
           <t>Euronics_IT</t>
         </is>
       </c>
-      <c r="G414" s="2" t="inlineStr">
-        <is>
-          <t>Digital Marketing Specialist</t>
-        </is>
-      </c>
+      <c r="G414" s="2" t="inlineStr"/>
       <c r="H414" s="2" t="inlineStr">
         <is>
-          <t>euronics.com</t>
-        </is>
-      </c>
-      <c r="I414" s="2" t="inlineStr">
-        <is>
-          <t>nl</t>
-        </is>
-      </c>
+          <t>euronics.it</t>
+        </is>
+      </c>
+      <c r="I414" s="2" t="inlineStr"/>
       <c r="J414" s="2" t="inlineStr">
         <is>
           <t>30 Giorni</t>
@@ -19189,7 +17569,7 @@
       <c r="G415" s="2" t="inlineStr"/>
       <c r="H415" s="2" t="inlineStr">
         <is>
-          <t>euronics.com</t>
+          <t>euronics.it</t>
         </is>
       </c>
       <c r="I415" s="2" t="inlineStr"/>
@@ -19204,43 +17584,23 @@
       <c r="R415" s="2" t="inlineStr"/>
     </row>
     <row r="416">
-      <c r="A416" s="3" t="inlineStr">
-        <is>
-          <t>Ivan</t>
-        </is>
-      </c>
-      <c r="B416" s="3" t="inlineStr">
-        <is>
-          <t>Valenzuela</t>
-        </is>
-      </c>
+      <c r="A416" s="3" t="inlineStr"/>
+      <c r="B416" s="3" t="inlineStr"/>
       <c r="C416" s="3" t="inlineStr"/>
       <c r="D416" s="3" t="inlineStr"/>
-      <c r="E416" s="5" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/ivan-valenzuela-76a257126</t>
-        </is>
-      </c>
+      <c r="E416" s="3" t="inlineStr"/>
       <c r="F416" s="3" t="inlineStr">
         <is>
           <t>Europcar IT</t>
         </is>
       </c>
-      <c r="G416" s="3" t="inlineStr">
-        <is>
-          <t>B2B Digital Marketing Manager</t>
-        </is>
-      </c>
+      <c r="G416" s="3" t="inlineStr"/>
       <c r="H416" s="3" t="inlineStr">
         <is>
-          <t>europcar.com</t>
-        </is>
-      </c>
-      <c r="I416" s="3" t="inlineStr">
-        <is>
-          <t>do</t>
-        </is>
-      </c>
+          <t>europcar.it</t>
+        </is>
+      </c>
+      <c r="I416" s="3" t="inlineStr"/>
       <c r="J416" s="3" t="inlineStr">
         <is>
           <t>30 Giorni</t>
@@ -19276,43 +17636,23 @@
       </c>
     </row>
     <row r="417">
-      <c r="A417" s="3" t="inlineStr">
-        <is>
-          <t>krishna</t>
-        </is>
-      </c>
-      <c r="B417" s="3" t="inlineStr">
-        <is>
-          <t>Balachandran</t>
-        </is>
-      </c>
+      <c r="A417" s="3" t="inlineStr"/>
+      <c r="B417" s="3" t="inlineStr"/>
       <c r="C417" s="3" t="inlineStr"/>
       <c r="D417" s="3" t="inlineStr"/>
-      <c r="E417" s="5" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/krishna-balachandran-652b43bb</t>
-        </is>
-      </c>
+      <c r="E417" s="3" t="inlineStr"/>
       <c r="F417" s="3" t="inlineStr">
         <is>
           <t>Europcar IT</t>
         </is>
       </c>
-      <c r="G417" s="3" t="inlineStr">
-        <is>
-          <t>Digital Marketing Specialist</t>
-        </is>
-      </c>
+      <c r="G417" s="3" t="inlineStr"/>
       <c r="H417" s="3" t="inlineStr">
         <is>
-          <t>europcar.com</t>
-        </is>
-      </c>
-      <c r="I417" s="3" t="inlineStr">
-        <is>
-          <t>qa</t>
-        </is>
-      </c>
+          <t>europcar.it</t>
+        </is>
+      </c>
+      <c r="I417" s="3" t="inlineStr"/>
       <c r="J417" s="3" t="inlineStr"/>
       <c r="K417" s="3" t="inlineStr"/>
       <c r="L417" s="3" t="inlineStr"/>
@@ -20436,43 +18776,23 @@
       <c r="R445" s="3" t="inlineStr"/>
     </row>
     <row r="446">
-      <c r="A446" s="2" t="inlineStr">
-        <is>
-          <t>Ilja</t>
-        </is>
-      </c>
-      <c r="B446" s="2" t="inlineStr">
-        <is>
-          <t>Vasiljevs</t>
-        </is>
-      </c>
+      <c r="A446" s="2" t="inlineStr"/>
+      <c r="B446" s="2" t="inlineStr"/>
       <c r="C446" s="2" t="inlineStr"/>
       <c r="D446" s="2" t="inlineStr"/>
-      <c r="E446" s="4" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/ilja-vasiljevs-a89144183</t>
-        </is>
-      </c>
+      <c r="E446" s="2" t="inlineStr"/>
       <c r="F446" s="2" t="inlineStr">
         <is>
           <t>Fifa Store IT</t>
         </is>
       </c>
-      <c r="G446" s="2" t="inlineStr">
-        <is>
-          <t>Affiliate Manager</t>
-        </is>
-      </c>
+      <c r="G446" s="2" t="inlineStr"/>
       <c r="H446" s="2" t="inlineStr">
         <is>
-          <t>fifa.com</t>
-        </is>
-      </c>
-      <c r="I446" s="2" t="inlineStr">
-        <is>
-          <t>gb</t>
-        </is>
-      </c>
+          <t>store.fifa.com</t>
+        </is>
+      </c>
+      <c r="I446" s="2" t="inlineStr"/>
       <c r="J446" s="2" t="inlineStr">
         <is>
           <t>30 Giorni</t>
@@ -20508,43 +18828,23 @@
       </c>
     </row>
     <row r="447">
-      <c r="A447" s="2" t="inlineStr">
-        <is>
-          <t>Trix</t>
-        </is>
-      </c>
-      <c r="B447" s="2" t="inlineStr">
-        <is>
-          <t>Schweizer-Hammer</t>
-        </is>
-      </c>
+      <c r="A447" s="2" t="inlineStr"/>
+      <c r="B447" s="2" t="inlineStr"/>
       <c r="C447" s="2" t="inlineStr"/>
       <c r="D447" s="2" t="inlineStr"/>
-      <c r="E447" s="4" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/trix-schweizer-hammer-2175b3a5</t>
-        </is>
-      </c>
+      <c r="E447" s="2" t="inlineStr"/>
       <c r="F447" s="2" t="inlineStr">
         <is>
           <t>Fifa Store IT</t>
         </is>
       </c>
-      <c r="G447" s="2" t="inlineStr">
-        <is>
-          <t>Senior Digital Marketing Project Manager</t>
-        </is>
-      </c>
+      <c r="G447" s="2" t="inlineStr"/>
       <c r="H447" s="2" t="inlineStr">
         <is>
-          <t>fifa.com</t>
-        </is>
-      </c>
-      <c r="I447" s="2" t="inlineStr">
-        <is>
-          <t>ch</t>
-        </is>
-      </c>
+          <t>store.fifa.com</t>
+        </is>
+      </c>
+      <c r="I447" s="2" t="inlineStr"/>
       <c r="J447" s="2" t="inlineStr"/>
       <c r="K447" s="2" t="inlineStr"/>
       <c r="L447" s="2" t="inlineStr"/>
@@ -20796,43 +19096,23 @@
       <c r="R453" s="3" t="inlineStr"/>
     </row>
     <row r="454">
-      <c r="A454" s="2" t="inlineStr">
-        <is>
-          <t>Lex</t>
-        </is>
-      </c>
-      <c r="B454" s="2" t="inlineStr">
-        <is>
-          <t>Camman</t>
-        </is>
-      </c>
+      <c r="A454" s="2" t="inlineStr"/>
+      <c r="B454" s="2" t="inlineStr"/>
       <c r="C454" s="2" t="inlineStr"/>
       <c r="D454" s="2" t="inlineStr"/>
-      <c r="E454" s="4" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/lex-camman-a29b0b282</t>
-        </is>
-      </c>
+      <c r="E454" s="2" t="inlineStr"/>
       <c r="F454" s="2" t="inlineStr">
         <is>
           <t>Fiverr Affiliates (Global Affiliate Program)</t>
         </is>
       </c>
-      <c r="G454" s="2" t="inlineStr">
-        <is>
-          <t>Digital Marketing Director</t>
-        </is>
-      </c>
+      <c r="G454" s="2" t="inlineStr"/>
       <c r="H454" s="2" t="inlineStr">
         <is>
           <t>fiverr.com</t>
         </is>
       </c>
-      <c r="I454" s="2" t="inlineStr">
-        <is>
-          <t>us</t>
-        </is>
-      </c>
+      <c r="I454" s="2" t="inlineStr"/>
       <c r="J454" s="2" t="inlineStr"/>
       <c r="K454" s="2" t="inlineStr">
         <is>
@@ -20868,43 +19148,23 @@
       </c>
     </row>
     <row r="455">
-      <c r="A455" s="2" t="inlineStr">
-        <is>
-          <t>MD</t>
-        </is>
-      </c>
-      <c r="B455" s="2" t="inlineStr">
-        <is>
-          <t>Saifullah</t>
-        </is>
-      </c>
+      <c r="A455" s="2" t="inlineStr"/>
+      <c r="B455" s="2" t="inlineStr"/>
       <c r="C455" s="2" t="inlineStr"/>
       <c r="D455" s="2" t="inlineStr"/>
-      <c r="E455" s="4" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/mdsaifullahofficial</t>
-        </is>
-      </c>
+      <c r="E455" s="2" t="inlineStr"/>
       <c r="F455" s="2" t="inlineStr">
         <is>
           <t>Fiverr Affiliates (Global Affiliate Program)</t>
         </is>
       </c>
-      <c r="G455" s="2" t="inlineStr">
-        <is>
-          <t>Digital Marketing Manager</t>
-        </is>
-      </c>
+      <c r="G455" s="2" t="inlineStr"/>
       <c r="H455" s="2" t="inlineStr">
         <is>
           <t>fiverr.com</t>
         </is>
       </c>
-      <c r="I455" s="2" t="inlineStr">
-        <is>
-          <t>us</t>
-        </is>
-      </c>
+      <c r="I455" s="2" t="inlineStr"/>
       <c r="J455" s="2" t="inlineStr"/>
       <c r="K455" s="2" t="inlineStr"/>
       <c r="L455" s="2" t="inlineStr"/>
@@ -20996,43 +19256,23 @@
       <c r="R457" s="3" t="inlineStr"/>
     </row>
     <row r="458">
-      <c r="A458" s="2" t="inlineStr">
-        <is>
-          <t>Kevin</t>
-        </is>
-      </c>
-      <c r="B458" s="2" t="inlineStr">
-        <is>
-          <t>Henao Saldarriaga</t>
-        </is>
-      </c>
+      <c r="A458" s="2" t="inlineStr"/>
+      <c r="B458" s="2" t="inlineStr"/>
       <c r="C458" s="2" t="inlineStr"/>
       <c r="D458" s="2" t="inlineStr"/>
-      <c r="E458" s="4" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/kevinhenaoupv</t>
-        </is>
-      </c>
+      <c r="E458" s="2" t="inlineStr"/>
       <c r="F458" s="2" t="inlineStr">
         <is>
           <t>Flibco Global</t>
         </is>
       </c>
-      <c r="G458" s="2" t="inlineStr">
-        <is>
-          <t>International Partnership &amp; Affiliate Manager</t>
-        </is>
-      </c>
+      <c r="G458" s="2" t="inlineStr"/>
       <c r="H458" s="2" t="inlineStr">
         <is>
           <t>flibco.com</t>
         </is>
       </c>
-      <c r="I458" s="2" t="inlineStr">
-        <is>
-          <t>lu</t>
-        </is>
-      </c>
+      <c r="I458" s="2" t="inlineStr"/>
       <c r="J458" s="2" t="inlineStr"/>
       <c r="K458" s="2" t="inlineStr">
         <is>
@@ -21064,43 +19304,23 @@
       </c>
     </row>
     <row r="459">
-      <c r="A459" s="2" t="inlineStr">
-        <is>
-          <t>Brenda</t>
-        </is>
-      </c>
-      <c r="B459" s="2" t="inlineStr">
-        <is>
-          <t>Hernández</t>
-        </is>
-      </c>
+      <c r="A459" s="2" t="inlineStr"/>
+      <c r="B459" s="2" t="inlineStr"/>
       <c r="C459" s="2" t="inlineStr"/>
       <c r="D459" s="2" t="inlineStr"/>
-      <c r="E459" s="4" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/brenda-hernández-795648171</t>
-        </is>
-      </c>
+      <c r="E459" s="2" t="inlineStr"/>
       <c r="F459" s="2" t="inlineStr">
         <is>
           <t>Flibco Global</t>
         </is>
       </c>
-      <c r="G459" s="2" t="inlineStr">
-        <is>
-          <t>Digital Marketing Specialist</t>
-        </is>
-      </c>
+      <c r="G459" s="2" t="inlineStr"/>
       <c r="H459" s="2" t="inlineStr">
         <is>
           <t>flibco.com</t>
         </is>
       </c>
-      <c r="I459" s="2" t="inlineStr">
-        <is>
-          <t>fr</t>
-        </is>
-      </c>
+      <c r="I459" s="2" t="inlineStr"/>
       <c r="J459" s="2" t="inlineStr"/>
       <c r="K459" s="2" t="inlineStr"/>
       <c r="L459" s="2" t="inlineStr"/>
@@ -21112,43 +19332,23 @@
       <c r="R459" s="2" t="inlineStr"/>
     </row>
     <row r="460">
-      <c r="A460" s="3" t="inlineStr">
-        <is>
-          <t>Courtney</t>
-        </is>
-      </c>
-      <c r="B460" s="3" t="inlineStr">
-        <is>
-          <t>Rand</t>
-        </is>
-      </c>
+      <c r="A460" s="3" t="inlineStr"/>
+      <c r="B460" s="3" t="inlineStr"/>
       <c r="C460" s="3" t="inlineStr"/>
       <c r="D460" s="3" t="inlineStr"/>
-      <c r="E460" s="5" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/courtney-rand-7a7a1110a</t>
-        </is>
-      </c>
+      <c r="E460" s="3" t="inlineStr"/>
       <c r="F460" s="3" t="inlineStr">
         <is>
           <t>Flightnetwork</t>
         </is>
       </c>
-      <c r="G460" s="3" t="inlineStr">
-        <is>
-          <t>Digital Marketing Manager</t>
-        </is>
-      </c>
+      <c r="G460" s="3" t="inlineStr"/>
       <c r="H460" s="3" t="inlineStr">
         <is>
-          <t>flightnetwork.com</t>
-        </is>
-      </c>
-      <c r="I460" s="3" t="inlineStr">
-        <is>
-          <t>ca</t>
-        </is>
-      </c>
+          <t>us-en.flightnetwork.com</t>
+        </is>
+      </c>
+      <c r="I460" s="3" t="inlineStr"/>
       <c r="J460" s="3" t="inlineStr"/>
       <c r="K460" s="3" t="inlineStr">
         <is>
@@ -21193,7 +19393,7 @@
       <c r="G461" s="3" t="inlineStr"/>
       <c r="H461" s="3" t="inlineStr">
         <is>
-          <t>flightnetwork.com</t>
+          <t>us-en.flightnetwork.com</t>
         </is>
       </c>
       <c r="I461" s="3" t="inlineStr"/>
@@ -21208,43 +19408,23 @@
       <c r="R461" s="3" t="inlineStr"/>
     </row>
     <row r="462">
-      <c r="A462" s="2" t="inlineStr">
-        <is>
-          <t>Haytham</t>
-        </is>
-      </c>
-      <c r="B462" s="2" t="inlineStr">
-        <is>
-          <t>El-Shamy</t>
-        </is>
-      </c>
+      <c r="A462" s="2" t="inlineStr"/>
+      <c r="B462" s="2" t="inlineStr"/>
       <c r="C462" s="2" t="inlineStr"/>
       <c r="D462" s="2" t="inlineStr"/>
-      <c r="E462" s="4" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/haythammagdy</t>
-        </is>
-      </c>
+      <c r="E462" s="2" t="inlineStr"/>
       <c r="F462" s="2" t="inlineStr">
         <is>
           <t>Flixbus IT</t>
         </is>
       </c>
-      <c r="G462" s="2" t="inlineStr">
-        <is>
-          <t>Global Head of Performance Marketing</t>
-        </is>
-      </c>
+      <c r="G462" s="2" t="inlineStr"/>
       <c r="H462" s="2" t="inlineStr">
         <is>
-          <t>flixbus.com</t>
-        </is>
-      </c>
-      <c r="I462" s="2" t="inlineStr">
-        <is>
-          <t>de</t>
-        </is>
-      </c>
+          <t>flixbus.it</t>
+        </is>
+      </c>
+      <c r="I462" s="2" t="inlineStr"/>
       <c r="J462" s="2" t="inlineStr">
         <is>
           <t>60 Giorni</t>
@@ -21280,43 +19460,23 @@
       </c>
     </row>
     <row r="463">
-      <c r="A463" s="2" t="inlineStr">
-        <is>
-          <t>Mónica</t>
-        </is>
-      </c>
-      <c r="B463" s="2" t="inlineStr">
-        <is>
-          <t>Casa Branca Santos</t>
-        </is>
-      </c>
+      <c r="A463" s="2" t="inlineStr"/>
+      <c r="B463" s="2" t="inlineStr"/>
       <c r="C463" s="2" t="inlineStr"/>
       <c r="D463" s="2" t="inlineStr"/>
-      <c r="E463" s="4" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/monicacasabranca</t>
-        </is>
-      </c>
+      <c r="E463" s="2" t="inlineStr"/>
       <c r="F463" s="2" t="inlineStr">
         <is>
           <t>Flixbus IT</t>
         </is>
       </c>
-      <c r="G463" s="2" t="inlineStr">
-        <is>
-          <t>Senior Performance Marketing Manager</t>
-        </is>
-      </c>
+      <c r="G463" s="2" t="inlineStr"/>
       <c r="H463" s="2" t="inlineStr">
         <is>
-          <t>flixbus.com</t>
-        </is>
-      </c>
-      <c r="I463" s="2" t="inlineStr">
-        <is>
-          <t>es</t>
-        </is>
-      </c>
+          <t>flixbus.it</t>
+        </is>
+      </c>
+      <c r="I463" s="2" t="inlineStr"/>
       <c r="J463" s="2" t="inlineStr"/>
       <c r="K463" s="2" t="inlineStr"/>
       <c r="L463" s="2" t="inlineStr"/>
@@ -21564,43 +19724,23 @@
       <c r="R469" s="3" t="inlineStr"/>
     </row>
     <row r="470">
-      <c r="A470" s="2" t="inlineStr">
-        <is>
-          <t>Sharon</t>
-        </is>
-      </c>
-      <c r="B470" s="2" t="inlineStr">
-        <is>
-          <t>Lewis</t>
-        </is>
-      </c>
+      <c r="A470" s="2" t="inlineStr"/>
+      <c r="B470" s="2" t="inlineStr"/>
       <c r="C470" s="2" t="inlineStr"/>
       <c r="D470" s="2" t="inlineStr"/>
-      <c r="E470" s="4" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/sharonlewisc</t>
-        </is>
-      </c>
+      <c r="E470" s="2" t="inlineStr"/>
       <c r="F470" s="2" t="inlineStr">
         <is>
           <t>Folletto IT</t>
         </is>
       </c>
-      <c r="G470" s="2" t="inlineStr">
-        <is>
-          <t>Global Head of Digital Marketing &amp; Business Transformation</t>
-        </is>
-      </c>
+      <c r="G470" s="2" t="inlineStr"/>
       <c r="H470" s="2" t="inlineStr">
         <is>
           <t>vorwerk.com</t>
         </is>
       </c>
-      <c r="I470" s="2" t="inlineStr">
-        <is>
-          <t>ch</t>
-        </is>
-      </c>
+      <c r="I470" s="2" t="inlineStr"/>
       <c r="J470" s="2" t="inlineStr">
         <is>
           <t>30 Giorni</t>
@@ -21636,43 +19776,23 @@
       </c>
     </row>
     <row r="471">
-      <c r="A471" s="2" t="inlineStr">
-        <is>
-          <t>Freya</t>
-        </is>
-      </c>
-      <c r="B471" s="2" t="inlineStr">
-        <is>
-          <t>Li</t>
-        </is>
-      </c>
+      <c r="A471" s="2" t="inlineStr"/>
+      <c r="B471" s="2" t="inlineStr"/>
       <c r="C471" s="2" t="inlineStr"/>
       <c r="D471" s="2" t="inlineStr"/>
-      <c r="E471" s="4" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/freya-li-60237938</t>
-        </is>
-      </c>
+      <c r="E471" s="2" t="inlineStr"/>
       <c r="F471" s="2" t="inlineStr">
         <is>
           <t>Folletto IT</t>
         </is>
       </c>
-      <c r="G471" s="2" t="inlineStr">
-        <is>
-          <t>Digital Marketing Manager</t>
-        </is>
-      </c>
+      <c r="G471" s="2" t="inlineStr"/>
       <c r="H471" s="2" t="inlineStr">
         <is>
           <t>vorwerk.com</t>
         </is>
       </c>
-      <c r="I471" s="2" t="inlineStr">
-        <is>
-          <t>cn</t>
-        </is>
-      </c>
+      <c r="I471" s="2" t="inlineStr"/>
       <c r="J471" s="2" t="inlineStr"/>
       <c r="K471" s="2" t="inlineStr"/>
       <c r="L471" s="2" t="inlineStr"/>
@@ -21684,43 +19804,23 @@
       <c r="R471" s="2" t="inlineStr"/>
     </row>
     <row r="472">
-      <c r="A472" s="3" t="inlineStr">
-        <is>
-          <t>Emmanuella</t>
-        </is>
-      </c>
-      <c r="B472" s="3" t="inlineStr">
-        <is>
-          <t>N.</t>
-        </is>
-      </c>
+      <c r="A472" s="3" t="inlineStr"/>
+      <c r="B472" s="3" t="inlineStr"/>
       <c r="C472" s="3" t="inlineStr"/>
       <c r="D472" s="3" t="inlineStr"/>
-      <c r="E472" s="5" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/emmanuella-nerantzoulis</t>
-        </is>
-      </c>
+      <c r="E472" s="3" t="inlineStr"/>
       <c r="F472" s="3" t="inlineStr">
         <is>
           <t>Foot Locker IT</t>
         </is>
       </c>
-      <c r="G472" s="3" t="inlineStr">
-        <is>
-          <t>Performance Marketing - Paid Social Coordinator</t>
-        </is>
-      </c>
+      <c r="G472" s="3" t="inlineStr"/>
       <c r="H472" s="3" t="inlineStr">
         <is>
-          <t>footlocker.com</t>
-        </is>
-      </c>
-      <c r="I472" s="3" t="inlineStr">
-        <is>
-          <t>nl</t>
-        </is>
-      </c>
+          <t>footlocker.it</t>
+        </is>
+      </c>
+      <c r="I472" s="3" t="inlineStr"/>
       <c r="J472" s="3" t="inlineStr">
         <is>
           <t>30 Giorni</t>
@@ -21769,7 +19869,7 @@
       <c r="G473" s="3" t="inlineStr"/>
       <c r="H473" s="3" t="inlineStr">
         <is>
-          <t>footlocker.com</t>
+          <t>footlocker.it</t>
         </is>
       </c>
       <c r="I473" s="3" t="inlineStr"/>
@@ -24346,43 +22446,23 @@
       <c r="R537" s="3" t="inlineStr"/>
     </row>
     <row r="538">
-      <c r="A538" s="2" t="inlineStr">
-        <is>
-          <t>Goldcar</t>
-        </is>
-      </c>
-      <c r="B538" s="2" t="inlineStr">
-        <is>
-          <t>Dubai</t>
-        </is>
-      </c>
+      <c r="A538" s="2" t="inlineStr"/>
+      <c r="B538" s="2" t="inlineStr"/>
       <c r="C538" s="2" t="inlineStr"/>
       <c r="D538" s="2" t="inlineStr"/>
-      <c r="E538" s="4" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/goldcar-dubai-b78866238</t>
-        </is>
-      </c>
+      <c r="E538" s="2" t="inlineStr"/>
       <c r="F538" s="2" t="inlineStr">
         <is>
           <t>Goldcar</t>
         </is>
       </c>
-      <c r="G538" s="2" t="inlineStr">
-        <is>
-          <t>Digital Marketing Manager</t>
-        </is>
-      </c>
+      <c r="G538" s="2" t="inlineStr"/>
       <c r="H538" s="2" t="inlineStr">
         <is>
           <t>goldcar.com</t>
         </is>
       </c>
-      <c r="I538" s="2" t="inlineStr">
-        <is>
-          <t>ae</t>
-        </is>
-      </c>
+      <c r="I538" s="2" t="inlineStr"/>
       <c r="J538" s="2" t="inlineStr"/>
       <c r="K538" s="2" t="inlineStr">
         <is>
@@ -26654,43 +24734,23 @@
       <c r="R595" s="2" t="inlineStr"/>
     </row>
     <row r="596">
-      <c r="A596" s="3" t="inlineStr">
-        <is>
-          <t>Maria</t>
-        </is>
-      </c>
-      <c r="B596" s="3" t="inlineStr">
-        <is>
-          <t>Shafranova</t>
-        </is>
-      </c>
+      <c r="A596" s="3" t="inlineStr"/>
+      <c r="B596" s="3" t="inlineStr"/>
       <c r="C596" s="3" t="inlineStr"/>
       <c r="D596" s="3" t="inlineStr"/>
-      <c r="E596" s="5" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/mariashafranova</t>
-        </is>
-      </c>
+      <c r="E596" s="3" t="inlineStr"/>
       <c r="F596" s="3" t="inlineStr">
         <is>
           <t>Holidu IT</t>
         </is>
       </c>
-      <c r="G596" s="3" t="inlineStr">
-        <is>
-          <t>Affiliate Marketing Manager</t>
-        </is>
-      </c>
+      <c r="G596" s="3" t="inlineStr"/>
       <c r="H596" s="3" t="inlineStr">
         <is>
-          <t>holidu.com</t>
-        </is>
-      </c>
-      <c r="I596" s="3" t="inlineStr">
-        <is>
-          <t>de</t>
-        </is>
-      </c>
+          <t>holidu.it</t>
+        </is>
+      </c>
+      <c r="I596" s="3" t="inlineStr"/>
       <c r="J596" s="3" t="inlineStr">
         <is>
           <t>30 Giorni</t>
@@ -26726,43 +24786,23 @@
       </c>
     </row>
     <row r="597">
-      <c r="A597" s="3" t="inlineStr">
-        <is>
-          <t>Tom</t>
-        </is>
-      </c>
-      <c r="B597" s="3" t="inlineStr">
-        <is>
-          <t>Salkeld</t>
-        </is>
-      </c>
+      <c r="A597" s="3" t="inlineStr"/>
+      <c r="B597" s="3" t="inlineStr"/>
       <c r="C597" s="3" t="inlineStr"/>
       <c r="D597" s="3" t="inlineStr"/>
-      <c r="E597" s="5" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/tom-salkeld-60228641</t>
-        </is>
-      </c>
+      <c r="E597" s="3" t="inlineStr"/>
       <c r="F597" s="3" t="inlineStr">
         <is>
           <t>Holidu IT</t>
         </is>
       </c>
-      <c r="G597" s="3" t="inlineStr">
-        <is>
-          <t>Senior Affiliate Partnership Manager</t>
-        </is>
-      </c>
+      <c r="G597" s="3" t="inlineStr"/>
       <c r="H597" s="3" t="inlineStr">
         <is>
-          <t>holidu.com</t>
-        </is>
-      </c>
-      <c r="I597" s="3" t="inlineStr">
-        <is>
-          <t>de</t>
-        </is>
-      </c>
+          <t>holidu.it</t>
+        </is>
+      </c>
+      <c r="I597" s="3" t="inlineStr"/>
       <c r="J597" s="3" t="inlineStr"/>
       <c r="K597" s="3" t="inlineStr"/>
       <c r="L597" s="3" t="inlineStr"/>
@@ -26854,43 +24894,23 @@
       <c r="R599" s="2" t="inlineStr"/>
     </row>
     <row r="600">
-      <c r="A600" s="3" t="inlineStr">
-        <is>
-          <t>Deni</t>
-        </is>
-      </c>
-      <c r="B600" s="3" t="inlineStr">
-        <is>
-          <t>Jelincic</t>
-        </is>
-      </c>
+      <c r="A600" s="3" t="inlineStr"/>
+      <c r="B600" s="3" t="inlineStr"/>
       <c r="C600" s="3" t="inlineStr"/>
       <c r="D600" s="3" t="inlineStr"/>
-      <c r="E600" s="5" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/djelincic</t>
-        </is>
-      </c>
+      <c r="E600" s="3" t="inlineStr"/>
       <c r="F600" s="3" t="inlineStr">
         <is>
           <t>Honor IT</t>
         </is>
       </c>
-      <c r="G600" s="3" t="inlineStr">
-        <is>
-          <t>Affiliate Marketing Manager</t>
-        </is>
-      </c>
+      <c r="G600" s="3" t="inlineStr"/>
       <c r="H600" s="3" t="inlineStr">
         <is>
           <t>honor.com</t>
         </is>
       </c>
-      <c r="I600" s="3" t="inlineStr">
-        <is>
-          <t>de</t>
-        </is>
-      </c>
+      <c r="I600" s="3" t="inlineStr"/>
       <c r="J600" s="3" t="inlineStr">
         <is>
           <t>30 Giorni</t>
@@ -26926,43 +24946,23 @@
       </c>
     </row>
     <row r="601">
-      <c r="A601" s="3" t="inlineStr">
-        <is>
-          <t>Imad</t>
-        </is>
-      </c>
-      <c r="B601" s="3" t="inlineStr">
-        <is>
-          <t>Hallaji</t>
-        </is>
-      </c>
+      <c r="A601" s="3" t="inlineStr"/>
+      <c r="B601" s="3" t="inlineStr"/>
       <c r="C601" s="3" t="inlineStr"/>
       <c r="D601" s="3" t="inlineStr"/>
-      <c r="E601" s="5" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/imadhallaji</t>
-        </is>
-      </c>
+      <c r="E601" s="3" t="inlineStr"/>
       <c r="F601" s="3" t="inlineStr">
         <is>
           <t>Honor IT</t>
         </is>
       </c>
-      <c r="G601" s="3" t="inlineStr">
-        <is>
-          <t>Digital Marketing Manager</t>
-        </is>
-      </c>
+      <c r="G601" s="3" t="inlineStr"/>
       <c r="H601" s="3" t="inlineStr">
         <is>
           <t>honor.com</t>
         </is>
       </c>
-      <c r="I601" s="3" t="inlineStr">
-        <is>
-          <t>ma</t>
-        </is>
-      </c>
+      <c r="I601" s="3" t="inlineStr"/>
       <c r="J601" s="3" t="inlineStr"/>
       <c r="K601" s="3" t="inlineStr"/>
       <c r="L601" s="3" t="inlineStr"/>
